--- a/r5-aist-trustworthyai-main/StructureDefinition-eu-ai-provenance.xlsx
+++ b/r5-aist-trustworthyai-main/StructureDefinition-eu-ai-provenance.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$70</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$71</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2618" uniqueCount="442">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2655" uniqueCount="448">
   <si>
     <t>Property</t>
   </si>
@@ -45,7 +45,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>EU AI Act Provenance (Human-in-the-Loop)</t>
+    <t>EU AI Provenance</t>
   </si>
   <si>
     <t>Status</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T08:40:47+00:00</t>
+    <t>2026-06-18T12:04:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -78,7 +78,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Records the execution of an AI system, including human oversight and data provenance.</t>
+    <t>A Provenance profile linking an AI-generated output to the contributing AI system, source data, and relevant processing or governance context.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -480,6 +480,22 @@
     <t>Categorizes the data processing as Primary Care or Secondary Use according to the EHDS.</t>
   </si>
   <si>
+    <t>Provenance.extension:secondaryUsePurpose</t>
+  </si>
+  <si>
+    <t>secondaryUsePurpose</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://example.org/fhir/eu-ai-transparency/StructureDefinition/ehds-secondary-use-purpose}
+</t>
+  </si>
+  <si>
+    <t>EHDS Secondary Use Purpose</t>
+  </si>
+  <si>
+    <t>Documents the permitted purpose for secondary use of electronic health data under the EHDS.</t>
+  </si>
+  <si>
     <t>Provenance.extension:dataPermit</t>
   </si>
   <si>
@@ -654,6 +670,9 @@
   <si>
     <t xml:space="preserve">PurposeOfEvent
 </t>
+  </si>
+  <si>
+    <t>2</t>
   </si>
   <si>
     <t xml:space="preserve">CodeableReference
@@ -1697,12 +1716,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO70"/>
+  <dimension ref="A1:AO71"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="56.2421875" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="44.3125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="12.81640625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="18.3125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
@@ -2932,7 +2951,7 @@
         <v>77</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>90</v>
@@ -3031,48 +3050,46 @@
         <v>18</v>
       </c>
     </row>
-    <row r="12" hidden="true">
+    <row r="12">
       <c r="A12" t="s" s="2">
         <v>153</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="C12" s="2"/>
+        <v>135</v>
+      </c>
+      <c r="C12" t="s" s="2">
+        <v>154</v>
+      </c>
       <c r="D12" t="s" s="2">
-        <v>154</v>
+        <v>18</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="H12" t="s" s="2">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="I12" t="s" s="2">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>136</v>
+        <v>155</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="N12" t="s" s="2">
         <v>157</v>
       </c>
-      <c r="O12" t="s" s="2">
-        <v>158</v>
-      </c>
+      <c r="N12" s="2"/>
+      <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
         <v>18</v>
       </c>
@@ -3120,7 +3137,7 @@
         <v>18</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>159</v>
+        <v>141</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>77</v>
@@ -3141,7 +3158,7 @@
         <v>18</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>134</v>
+        <v>18</v>
       </c>
       <c r="AN12" t="s" s="2">
         <v>18</v>
@@ -3150,46 +3167,48 @@
         <v>18</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>18</v>
+        <v>159</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="G13" t="s" s="2">
         <v>78</v>
       </c>
       <c r="H13" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I13" t="s" s="2">
         <v>90</v>
-      </c>
-      <c r="I13" t="s" s="2">
-        <v>18</v>
       </c>
       <c r="J13" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K13" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="L13" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="M13" t="s" s="2">
         <v>161</v>
       </c>
-      <c r="L13" t="s" s="2">
+      <c r="N13" t="s" s="2">
         <v>162</v>
       </c>
-      <c r="M13" t="s" s="2">
+      <c r="O13" t="s" s="2">
         <v>163</v>
       </c>
-      <c r="N13" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
         <v>18</v>
       </c>
@@ -3237,10 +3256,10 @@
         <v>18</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="AG13" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="AH13" t="s" s="2">
         <v>78</v>
@@ -3249,30 +3268,30 @@
         <v>18</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>101</v>
+        <v>142</v>
       </c>
       <c r="AK13" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>165</v>
+        <v>18</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>166</v>
+        <v>134</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>167</v>
+        <v>18</v>
       </c>
       <c r="AO13" t="s" s="2">
-        <v>168</v>
+        <v>18</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3283,7 +3302,7 @@
         <v>89</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>90</v>
@@ -3292,19 +3311,19 @@
         <v>18</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3354,13 +3373,13 @@
         <v>18</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>18</v>
@@ -3369,27 +3388,27 @@
         <v>101</v>
       </c>
       <c r="AK14" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AL14" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="AM14" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="AN14" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="AO14" t="s" s="2">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="2">
         <v>174</v>
       </c>
-      <c r="AL14" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="AM14" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="AN14" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="AO14" t="s" s="2">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="15" hidden="true">
-      <c r="A15" t="s" s="2">
-        <v>178</v>
-      </c>
       <c r="B15" t="s" s="2">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3397,31 +3416,31 @@
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="G15" t="s" s="2">
         <v>89</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="I15" t="s" s="2">
         <v>18</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3471,7 +3490,7 @@
         <v>18</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>77</v>
@@ -3486,27 +3505,27 @@
         <v>101</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>18</v>
+        <v>179</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="AO15" t="s" s="2">
-        <v>186</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3517,7 +3536,7 @@
         <v>77</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>18</v>
@@ -3526,19 +3545,19 @@
         <v>18</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>103</v>
+        <v>184</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -3588,13 +3607,13 @@
         <v>18</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>18</v>
@@ -3606,24 +3625,24 @@
         <v>18</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>18</v>
+        <v>188</v>
       </c>
       <c r="AM16" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="AN16" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="AO16" t="s" s="2">
         <v>191</v>
-      </c>
-      <c r="AN16" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AO16" t="s" s="2">
-        <v>192</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3634,7 +3653,7 @@
         <v>77</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>18</v>
@@ -3646,15 +3665,17 @@
         <v>18</v>
       </c>
       <c r="K17" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="L17" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="M17" t="s" s="2">
         <v>194</v>
       </c>
-      <c r="L17" t="s" s="2">
+      <c r="N17" t="s" s="2">
         <v>195</v>
       </c>
-      <c r="M17" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="N17" s="2"/>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>18</v>
@@ -3703,13 +3724,13 @@
         <v>18</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>18</v>
@@ -3718,41 +3739,41 @@
         <v>101</v>
       </c>
       <c r="AK17" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AL17" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AM17" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="AN17" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AO17" t="s" s="2">
         <v>197</v>
-      </c>
-      <c r="AL17" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="AM17" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="AN17" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="AO17" t="s" s="2">
-        <v>201</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>203</v>
+        <v>18</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="I18" t="s" s="2">
         <v>18</v>
@@ -3761,18 +3782,16 @@
         <v>18</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="N18" s="2"/>
-      <c r="O18" t="s" s="2">
-        <v>207</v>
-      </c>
+      <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>18</v>
       </c>
@@ -3796,35 +3815,37 @@
         <v>18</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>208</v>
+        <v>18</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>209</v>
+        <v>18</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>210</v>
+        <v>18</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="AC18" s="2"/>
+        <v>18</v>
+      </c>
+      <c r="AC18" t="s" s="2">
+        <v>18</v>
+      </c>
       <c r="AD18" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>140</v>
+        <v>18</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>18</v>
@@ -3833,40 +3854,38 @@
         <v>101</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>212</v>
+        <v>202</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>214</v>
+        <v>204</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>215</v>
+        <v>205</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>216</v>
+        <v>206</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>217</v>
+        <v>207</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="C19" t="s" s="2">
-        <v>218</v>
-      </c>
+        <v>207</v>
+      </c>
+      <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>89</v>
+        <v>209</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>90</v>
@@ -3878,17 +3897,17 @@
         <v>18</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" t="s" s="2">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>18</v>
@@ -3913,29 +3932,29 @@
         <v>18</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="Y19" s="2"/>
+        <v>214</v>
+      </c>
+      <c r="Y19" t="s" s="2">
+        <v>215</v>
+      </c>
       <c r="Z19" t="s" s="2">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AC19" t="s" s="2">
-        <v>18</v>
-      </c>
+        <v>217</v>
+      </c>
+      <c r="AC19" s="2"/>
       <c r="AD19" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>18</v>
+        <v>140</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>77</v>
@@ -3950,41 +3969,43 @@
         <v>101</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>216</v>
+        <v>222</v>
       </c>
     </row>
-    <row r="20" hidden="true">
+    <row r="20">
       <c r="A20" t="s" s="2">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="C20" s="2"/>
+        <v>207</v>
+      </c>
+      <c r="C20" t="s" s="2">
+        <v>224</v>
+      </c>
       <c r="D20" t="s" s="2">
-        <v>18</v>
+        <v>208</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="G20" t="s" s="2">
         <v>89</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="I20" t="s" s="2">
         <v>18</v>
@@ -3993,16 +4014,18 @@
         <v>18</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>91</v>
+        <v>210</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>222</v>
+        <v>211</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>223</v>
+        <v>212</v>
       </c>
       <c r="N20" s="2"/>
-      <c r="O20" s="2"/>
+      <c r="O20" t="s" s="2">
+        <v>213</v>
+      </c>
       <c r="P20" t="s" s="2">
         <v>18</v>
       </c>
@@ -4026,13 +4049,11 @@
         <v>18</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="Y20" t="s" s="2">
-        <v>18</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="Y20" s="2"/>
       <c r="Z20" t="s" s="2">
-        <v>18</v>
+        <v>225</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>18</v>
@@ -4050,53 +4071,53 @@
         <v>18</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>224</v>
+        <v>207</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>225</v>
+        <v>18</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>18</v>
+        <v>101</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>18</v>
+        <v>218</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>18</v>
+        <v>219</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>18</v>
+        <v>221</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>18</v>
+        <v>222</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="B21" t="s" s="2">
         <v>227</v>
-      </c>
-      <c r="B21" t="s" s="2">
-        <v>228</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>154</v>
+        <v>18</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>18</v>
@@ -4108,17 +4129,15 @@
         <v>18</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>136</v>
+        <v>91</v>
       </c>
       <c r="L21" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="M21" t="s" s="2">
         <v>229</v>
       </c>
-      <c r="M21" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>157</v>
-      </c>
+      <c r="N21" s="2"/>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>18</v>
@@ -4155,40 +4174,40 @@
         <v>18</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>139</v>
+        <v>18</v>
       </c>
       <c r="AC21" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AD21" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AE21" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AF21" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="AG21" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH21" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI21" t="s" s="2">
         <v>231</v>
       </c>
-      <c r="AD21" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AE21" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="AF21" t="s" s="2">
+      <c r="AJ21" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AK21" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AL21" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AM21" t="s" s="2">
         <v>232</v>
-      </c>
-      <c r="AG21" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH21" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI21" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AJ21" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="AK21" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AL21" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AM21" t="s" s="2">
-        <v>226</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>18</v>
@@ -4206,14 +4225,14 @@
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>18</v>
+        <v>159</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>18</v>
@@ -4222,18 +4241,20 @@
         <v>18</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="K22" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="L22" t="s" s="2">
         <v>235</v>
       </c>
-      <c r="L22" t="s" s="2">
+      <c r="M22" t="s" s="2">
         <v>236</v>
       </c>
-      <c r="M22" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="N22" s="2"/>
+      <c r="N22" t="s" s="2">
+        <v>162</v>
+      </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>18</v>
@@ -4270,16 +4291,16 @@
         <v>18</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>18</v>
+        <v>139</v>
       </c>
       <c r="AC22" t="s" s="2">
-        <v>18</v>
+        <v>237</v>
       </c>
       <c r="AD22" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>18</v>
+        <v>140</v>
       </c>
       <c r="AF22" t="s" s="2">
         <v>238</v>
@@ -4288,13 +4309,13 @@
         <v>77</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>101</v>
+        <v>142</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>18</v>
@@ -4303,7 +4324,7 @@
         <v>18</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>134</v>
+        <v>232</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>18</v>
@@ -4325,7 +4346,7 @@
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="G23" t="s" s="2">
         <v>89</v>
@@ -4337,16 +4358,16 @@
         <v>18</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>91</v>
+        <v>241</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>222</v>
+        <v>242</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>223</v>
+        <v>243</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -4397,7 +4418,7 @@
         <v>18</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>224</v>
+        <v>244</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>77</v>
@@ -4406,10 +4427,10 @@
         <v>89</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>225</v>
+        <v>18</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>18</v>
+        <v>101</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>18</v>
@@ -4418,7 +4439,7 @@
         <v>18</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>226</v>
+        <v>134</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>18</v>
@@ -4429,21 +4450,21 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>154</v>
+        <v>18</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>18</v>
@@ -4455,17 +4476,15 @@
         <v>18</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>136</v>
+        <v>91</v>
       </c>
       <c r="L24" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="M24" t="s" s="2">
         <v>229</v>
       </c>
-      <c r="M24" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>157</v>
-      </c>
+      <c r="N24" s="2"/>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>18</v>
@@ -4502,40 +4521,40 @@
         <v>18</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>139</v>
+        <v>18</v>
       </c>
       <c r="AC24" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AD24" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AE24" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AF24" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="AG24" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH24" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI24" t="s" s="2">
         <v>231</v>
       </c>
-      <c r="AD24" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AE24" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="AF24" t="s" s="2">
+      <c r="AJ24" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AK24" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AL24" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AM24" t="s" s="2">
         <v>232</v>
-      </c>
-      <c r="AG24" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH24" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI24" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AJ24" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="AK24" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AL24" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AM24" t="s" s="2">
-        <v>226</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>18</v>
@@ -4546,14 +4565,14 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>18</v>
+        <v>159</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -4569,23 +4588,21 @@
         <v>18</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>245</v>
+        <v>136</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>246</v>
+        <v>235</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>247</v>
+        <v>236</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>249</v>
-      </c>
+        <v>162</v>
+      </c>
+      <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>18</v>
       </c>
@@ -4621,19 +4638,19 @@
         <v>18</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>18</v>
+        <v>139</v>
       </c>
       <c r="AC25" t="s" s="2">
-        <v>18</v>
+        <v>237</v>
       </c>
       <c r="AD25" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>18</v>
+        <v>140</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>77</v>
@@ -4645,7 +4662,7 @@
         <v>18</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>101</v>
+        <v>142</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>18</v>
@@ -4654,7 +4671,7 @@
         <v>18</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>251</v>
+        <v>232</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>18</v>
@@ -4665,10 +4682,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4679,7 +4696,7 @@
         <v>77</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>18</v>
@@ -4688,19 +4705,23 @@
         <v>18</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>91</v>
+        <v>251</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>222</v>
+        <v>252</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="N26" s="2"/>
-      <c r="O26" s="2"/>
+        <v>253</v>
+      </c>
+      <c r="N26" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="O26" t="s" s="2">
+        <v>255</v>
+      </c>
       <c r="P26" t="s" s="2">
         <v>18</v>
       </c>
@@ -4748,19 +4769,19 @@
         <v>18</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>225</v>
+        <v>18</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>18</v>
+        <v>101</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>18</v>
@@ -4769,7 +4790,7 @@
         <v>18</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>226</v>
+        <v>257</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>18</v>
@@ -4780,21 +4801,21 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>154</v>
+        <v>18</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>18</v>
@@ -4806,17 +4827,15 @@
         <v>18</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>136</v>
+        <v>91</v>
       </c>
       <c r="L27" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="M27" t="s" s="2">
         <v>229</v>
       </c>
-      <c r="M27" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>157</v>
-      </c>
+      <c r="N27" s="2"/>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>18</v>
@@ -4853,40 +4872,40 @@
         <v>18</v>
       </c>
       <c r="AB27" t="s" s="2">
-        <v>139</v>
+        <v>18</v>
       </c>
       <c r="AC27" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AD27" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AE27" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AF27" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="AG27" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH27" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI27" t="s" s="2">
         <v>231</v>
       </c>
-      <c r="AD27" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AE27" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="AF27" t="s" s="2">
+      <c r="AJ27" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AK27" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AL27" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AM27" t="s" s="2">
         <v>232</v>
-      </c>
-      <c r="AG27" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH27" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI27" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AJ27" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="AK27" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AL27" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AM27" t="s" s="2">
-        <v>226</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>18</v>
@@ -4897,21 +4916,21 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>18</v>
+        <v>159</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>18</v>
@@ -4920,23 +4939,21 @@
         <v>18</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>103</v>
+        <v>136</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>258</v>
+        <v>235</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>259</v>
+        <v>236</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>260</v>
-      </c>
-      <c r="O28" t="s" s="2">
-        <v>261</v>
-      </c>
+        <v>162</v>
+      </c>
+      <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>18</v>
       </c>
@@ -4945,7 +4962,7 @@
         <v>18</v>
       </c>
       <c r="S28" t="s" s="2">
-        <v>262</v>
+        <v>18</v>
       </c>
       <c r="T28" t="s" s="2">
         <v>18</v>
@@ -4972,31 +4989,31 @@
         <v>18</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>18</v>
+        <v>139</v>
       </c>
       <c r="AC28" t="s" s="2">
-        <v>18</v>
+        <v>237</v>
       </c>
       <c r="AD28" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>18</v>
+        <v>140</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>263</v>
+        <v>238</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>101</v>
+        <v>142</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>18</v>
@@ -5005,7 +5022,7 @@
         <v>18</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>264</v>
+        <v>232</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>18</v>
@@ -5016,10 +5033,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5027,7 +5044,7 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="G29" t="s" s="2">
         <v>89</v>
@@ -5042,18 +5059,20 @@
         <v>90</v>
       </c>
       <c r="K29" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="L29" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="M29" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="N29" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="O29" t="s" s="2">
         <v>267</v>
       </c>
-      <c r="L29" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="M29" t="s" s="2">
-        <v>269</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>270</v>
-      </c>
-      <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>18</v>
       </c>
@@ -5062,7 +5081,7 @@
         <v>18</v>
       </c>
       <c r="S29" t="s" s="2">
-        <v>18</v>
+        <v>268</v>
       </c>
       <c r="T29" t="s" s="2">
         <v>18</v>
@@ -5101,7 +5120,7 @@
         <v>18</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>77</v>
@@ -5122,7 +5141,7 @@
         <v>18</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>18</v>
@@ -5133,10 +5152,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5159,18 +5178,18 @@
         <v>90</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>109</v>
+        <v>273</v>
       </c>
       <c r="L30" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="M30" t="s" s="2">
         <v>275</v>
       </c>
-      <c r="M30" t="s" s="2">
+      <c r="N30" t="s" s="2">
         <v>276</v>
       </c>
-      <c r="N30" s="2"/>
-      <c r="O30" t="s" s="2">
-        <v>277</v>
-      </c>
+      <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>18</v>
       </c>
@@ -5218,7 +5237,7 @@
         <v>18</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>77</v>
@@ -5227,7 +5246,7 @@
         <v>89</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>279</v>
+        <v>18</v>
       </c>
       <c r="AJ30" t="s" s="2">
         <v>101</v>
@@ -5239,7 +5258,7 @@
         <v>18</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>18</v>
@@ -5250,10 +5269,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5276,17 +5295,17 @@
         <v>90</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>267</v>
+        <v>109</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" t="s" s="2">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>18</v>
@@ -5335,7 +5354,7 @@
         <v>18</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>77</v>
@@ -5344,7 +5363,7 @@
         <v>89</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="AJ31" t="s" s="2">
         <v>101</v>
@@ -5356,7 +5375,7 @@
         <v>18</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>18</v>
@@ -5367,10 +5386,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="B32" t="s" s="2">
         <v>288</v>
-      </c>
-      <c r="B32" t="s" s="2">
-        <v>289</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5393,19 +5412,17 @@
         <v>90</v>
       </c>
       <c r="K32" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="L32" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="M32" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="L32" t="s" s="2">
+      <c r="N32" s="2"/>
+      <c r="O32" t="s" s="2">
         <v>291</v>
-      </c>
-      <c r="M32" t="s" s="2">
-        <v>292</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="O32" t="s" s="2">
-        <v>294</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>18</v>
@@ -5454,7 +5471,7 @@
         <v>18</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>77</v>
@@ -5463,7 +5480,7 @@
         <v>89</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>18</v>
+        <v>285</v>
       </c>
       <c r="AJ32" t="s" s="2">
         <v>101</v>
@@ -5475,7 +5492,7 @@
         <v>18</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>18</v>
@@ -5486,10 +5503,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5512,19 +5529,19 @@
         <v>90</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>267</v>
+        <v>296</v>
       </c>
       <c r="L33" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="M33" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="N33" t="s" s="2">
         <v>299</v>
       </c>
-      <c r="M33" t="s" s="2">
+      <c r="O33" t="s" s="2">
         <v>300</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="O33" t="s" s="2">
-        <v>302</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>18</v>
@@ -5573,7 +5590,7 @@
         <v>18</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>77</v>
@@ -5594,7 +5611,7 @@
         <v>18</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>18</v>
@@ -5605,10 +5622,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5631,16 +5648,20 @@
         <v>90</v>
       </c>
       <c r="K34" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="L34" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="M34" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="N34" t="s" s="2">
         <v>307</v>
       </c>
-      <c r="L34" t="s" s="2">
+      <c r="O34" t="s" s="2">
         <v>308</v>
       </c>
-      <c r="M34" t="s" s="2">
-        <v>309</v>
-      </c>
-      <c r="N34" s="2"/>
-      <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>18</v>
       </c>
@@ -5688,7 +5709,7 @@
         <v>18</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>77</v>
@@ -5709,7 +5730,7 @@
         <v>18</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>134</v>
+        <v>310</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>18</v>
@@ -5718,18 +5739,16 @@
         <v>18</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
         <v>311</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="C35" t="s" s="2">
         <v>312</v>
       </c>
+      <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>203</v>
+        <v>18</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -5739,27 +5758,25 @@
         <v>89</v>
       </c>
       <c r="H35" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I35" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J35" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="I35" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="J35" t="s" s="2">
-        <v>18</v>
-      </c>
       <c r="K35" t="s" s="2">
-        <v>204</v>
+        <v>313</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>205</v>
+        <v>314</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>206</v>
+        <v>315</v>
       </c>
       <c r="N35" s="2"/>
-      <c r="O35" t="s" s="2">
-        <v>207</v>
-      </c>
+      <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>18</v>
       </c>
@@ -5783,11 +5800,13 @@
         <v>18</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="Y35" s="2"/>
+        <v>18</v>
+      </c>
+      <c r="Y35" t="s" s="2">
+        <v>18</v>
+      </c>
       <c r="Z35" t="s" s="2">
-        <v>313</v>
+        <v>18</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>18</v>
@@ -5805,13 +5824,13 @@
         <v>18</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>202</v>
+        <v>316</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>18</v>
@@ -5820,41 +5839,43 @@
         <v>101</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>212</v>
+        <v>18</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>213</v>
+        <v>18</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>214</v>
+        <v>134</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>215</v>
+        <v>18</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>216</v>
+        <v>18</v>
       </c>
     </row>
-    <row r="36" hidden="true">
+    <row r="36">
       <c r="A36" t="s" s="2">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="C36" s="2"/>
+        <v>207</v>
+      </c>
+      <c r="C36" t="s" s="2">
+        <v>318</v>
+      </c>
       <c r="D36" t="s" s="2">
-        <v>18</v>
+        <v>208</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="G36" t="s" s="2">
         <v>89</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>18</v>
@@ -5863,16 +5884,18 @@
         <v>18</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>91</v>
+        <v>210</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>222</v>
+        <v>211</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>223</v>
+        <v>212</v>
       </c>
       <c r="N36" s="2"/>
-      <c r="O36" s="2"/>
+      <c r="O36" t="s" s="2">
+        <v>213</v>
+      </c>
       <c r="P36" t="s" s="2">
         <v>18</v>
       </c>
@@ -5896,13 +5919,11 @@
         <v>18</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="Y36" t="s" s="2">
-        <v>18</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="Y36" s="2"/>
       <c r="Z36" t="s" s="2">
-        <v>18</v>
+        <v>319</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>18</v>
@@ -5920,53 +5941,53 @@
         <v>18</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>224</v>
+        <v>207</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>225</v>
+        <v>18</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>18</v>
+        <v>101</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>18</v>
+        <v>218</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>18</v>
+        <v>219</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>18</v>
+        <v>221</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>18</v>
+        <v>222</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>154</v>
+        <v>18</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>18</v>
@@ -5978,17 +5999,15 @@
         <v>18</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>136</v>
+        <v>91</v>
       </c>
       <c r="L37" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="M37" t="s" s="2">
         <v>229</v>
       </c>
-      <c r="M37" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>157</v>
-      </c>
+      <c r="N37" s="2"/>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>18</v>
@@ -6025,40 +6044,40 @@
         <v>18</v>
       </c>
       <c r="AB37" t="s" s="2">
-        <v>139</v>
+        <v>18</v>
       </c>
       <c r="AC37" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AD37" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AE37" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AF37" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="AG37" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH37" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI37" t="s" s="2">
         <v>231</v>
       </c>
-      <c r="AD37" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AE37" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="AF37" t="s" s="2">
+      <c r="AJ37" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AK37" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AL37" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AM37" t="s" s="2">
         <v>232</v>
-      </c>
-      <c r="AG37" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH37" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI37" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AJ37" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="AK37" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AL37" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AM37" t="s" s="2">
-        <v>226</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>18</v>
@@ -6069,21 +6088,21 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="B38" t="s" s="2">
         <v>234</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>18</v>
+        <v>159</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>18</v>
@@ -6092,18 +6111,20 @@
         <v>18</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="K38" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="L38" t="s" s="2">
         <v>235</v>
       </c>
-      <c r="L38" t="s" s="2">
+      <c r="M38" t="s" s="2">
         <v>236</v>
       </c>
-      <c r="M38" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="N38" s="2"/>
+      <c r="N38" t="s" s="2">
+        <v>162</v>
+      </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>18</v>
@@ -6140,16 +6161,16 @@
         <v>18</v>
       </c>
       <c r="AB38" t="s" s="2">
-        <v>18</v>
+        <v>139</v>
       </c>
       <c r="AC38" t="s" s="2">
-        <v>18</v>
+        <v>237</v>
       </c>
       <c r="AD38" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AE38" t="s" s="2">
-        <v>18</v>
+        <v>140</v>
       </c>
       <c r="AF38" t="s" s="2">
         <v>238</v>
@@ -6158,13 +6179,13 @@
         <v>77</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>101</v>
+        <v>142</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>18</v>
@@ -6173,7 +6194,7 @@
         <v>18</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>134</v>
+        <v>232</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>18</v>
@@ -6184,7 +6205,7 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="B39" t="s" s="2">
         <v>240</v>
@@ -6195,7 +6216,7 @@
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="G39" t="s" s="2">
         <v>89</v>
@@ -6207,16 +6228,16 @@
         <v>18</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>91</v>
+        <v>241</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>222</v>
+        <v>242</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>223</v>
+        <v>243</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -6267,7 +6288,7 @@
         <v>18</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>224</v>
+        <v>244</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>77</v>
@@ -6276,10 +6297,10 @@
         <v>89</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>225</v>
+        <v>18</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>18</v>
+        <v>101</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>18</v>
@@ -6288,7 +6309,7 @@
         <v>18</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>226</v>
+        <v>134</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>18</v>
@@ -6299,21 +6320,21 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>154</v>
+        <v>18</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>18</v>
@@ -6325,17 +6346,15 @@
         <v>18</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>136</v>
+        <v>91</v>
       </c>
       <c r="L40" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="M40" t="s" s="2">
         <v>229</v>
       </c>
-      <c r="M40" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>157</v>
-      </c>
+      <c r="N40" s="2"/>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>18</v>
@@ -6372,40 +6391,40 @@
         <v>18</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>139</v>
+        <v>18</v>
       </c>
       <c r="AC40" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AD40" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AE40" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AF40" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="AG40" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH40" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI40" t="s" s="2">
         <v>231</v>
       </c>
-      <c r="AD40" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AE40" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="AF40" t="s" s="2">
+      <c r="AJ40" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AK40" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AL40" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AM40" t="s" s="2">
         <v>232</v>
-      </c>
-      <c r="AG40" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH40" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI40" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AJ40" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="AK40" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AL40" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AM40" t="s" s="2">
-        <v>226</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>18</v>
@@ -6416,14 +6435,14 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>18</v>
+        <v>159</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -6439,23 +6458,21 @@
         <v>18</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>245</v>
+        <v>136</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>246</v>
+        <v>235</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>247</v>
+        <v>236</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>249</v>
-      </c>
+        <v>162</v>
+      </c>
+      <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>18</v>
       </c>
@@ -6491,19 +6508,19 @@
         <v>18</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>18</v>
+        <v>139</v>
       </c>
       <c r="AC41" t="s" s="2">
-        <v>18</v>
+        <v>237</v>
       </c>
       <c r="AD41" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>18</v>
+        <v>140</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>77</v>
@@ -6515,7 +6532,7 @@
         <v>18</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>101</v>
+        <v>142</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>18</v>
@@ -6524,7 +6541,7 @@
         <v>18</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>251</v>
+        <v>232</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>18</v>
@@ -6535,10 +6552,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6549,7 +6566,7 @@
         <v>77</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>18</v>
@@ -6558,19 +6575,23 @@
         <v>18</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>91</v>
+        <v>251</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>222</v>
+        <v>252</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="N42" s="2"/>
-      <c r="O42" s="2"/>
+        <v>253</v>
+      </c>
+      <c r="N42" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="O42" t="s" s="2">
+        <v>255</v>
+      </c>
       <c r="P42" t="s" s="2">
         <v>18</v>
       </c>
@@ -6618,19 +6639,19 @@
         <v>18</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>225</v>
+        <v>18</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>18</v>
+        <v>101</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>18</v>
@@ -6639,7 +6660,7 @@
         <v>18</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>226</v>
+        <v>257</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>18</v>
@@ -6650,21 +6671,21 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>154</v>
+        <v>18</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>18</v>
@@ -6676,17 +6697,15 @@
         <v>18</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>136</v>
+        <v>91</v>
       </c>
       <c r="L43" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="M43" t="s" s="2">
         <v>229</v>
       </c>
-      <c r="M43" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>157</v>
-      </c>
+      <c r="N43" s="2"/>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>18</v>
@@ -6723,40 +6742,40 @@
         <v>18</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>139</v>
+        <v>18</v>
       </c>
       <c r="AC43" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AD43" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AE43" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AF43" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="AG43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH43" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI43" t="s" s="2">
         <v>231</v>
       </c>
-      <c r="AD43" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AE43" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="AF43" t="s" s="2">
+      <c r="AJ43" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AK43" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AL43" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AM43" t="s" s="2">
         <v>232</v>
-      </c>
-      <c r="AG43" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH43" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI43" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AJ43" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="AK43" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AL43" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AM43" t="s" s="2">
-        <v>226</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>18</v>
@@ -6767,21 +6786,21 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>18</v>
+        <v>159</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>18</v>
@@ -6790,23 +6809,21 @@
         <v>18</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>103</v>
+        <v>136</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>258</v>
+        <v>235</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>259</v>
+        <v>236</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>260</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>261</v>
-      </c>
+        <v>162</v>
+      </c>
+      <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>18</v>
       </c>
@@ -6815,7 +6832,7 @@
         <v>18</v>
       </c>
       <c r="S44" t="s" s="2">
-        <v>323</v>
+        <v>18</v>
       </c>
       <c r="T44" t="s" s="2">
         <v>18</v>
@@ -6842,31 +6859,31 @@
         <v>18</v>
       </c>
       <c r="AB44" t="s" s="2">
-        <v>18</v>
+        <v>139</v>
       </c>
       <c r="AC44" t="s" s="2">
-        <v>18</v>
+        <v>237</v>
       </c>
       <c r="AD44" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AE44" t="s" s="2">
-        <v>18</v>
+        <v>140</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>263</v>
+        <v>238</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>101</v>
+        <v>142</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>18</v>
@@ -6875,7 +6892,7 @@
         <v>18</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>264</v>
+        <v>232</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>18</v>
@@ -6886,10 +6903,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6897,7 +6914,7 @@
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="G45" t="s" s="2">
         <v>89</v>
@@ -6912,18 +6929,20 @@
         <v>90</v>
       </c>
       <c r="K45" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="L45" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="M45" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="O45" t="s" s="2">
         <v>267</v>
       </c>
-      <c r="L45" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>269</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>270</v>
-      </c>
-      <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>18</v>
       </c>
@@ -6932,7 +6951,7 @@
         <v>18</v>
       </c>
       <c r="S45" t="s" s="2">
-        <v>18</v>
+        <v>329</v>
       </c>
       <c r="T45" t="s" s="2">
         <v>18</v>
@@ -6971,7 +6990,7 @@
         <v>18</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>77</v>
@@ -6992,7 +7011,7 @@
         <v>18</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>18</v>
@@ -7003,10 +7022,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7029,18 +7048,18 @@
         <v>90</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>109</v>
+        <v>273</v>
       </c>
       <c r="L46" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="M46" t="s" s="2">
         <v>275</v>
       </c>
-      <c r="M46" t="s" s="2">
+      <c r="N46" t="s" s="2">
         <v>276</v>
       </c>
-      <c r="N46" s="2"/>
-      <c r="O46" t="s" s="2">
-        <v>277</v>
-      </c>
+      <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>18</v>
       </c>
@@ -7088,7 +7107,7 @@
         <v>18</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>77</v>
@@ -7097,7 +7116,7 @@
         <v>89</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>279</v>
+        <v>18</v>
       </c>
       <c r="AJ46" t="s" s="2">
         <v>101</v>
@@ -7109,7 +7128,7 @@
         <v>18</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>18</v>
@@ -7120,10 +7139,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7146,17 +7165,17 @@
         <v>90</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>267</v>
+        <v>109</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" t="s" s="2">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>18</v>
@@ -7205,7 +7224,7 @@
         <v>18</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>77</v>
@@ -7214,7 +7233,7 @@
         <v>89</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="AJ47" t="s" s="2">
         <v>101</v>
@@ -7226,7 +7245,7 @@
         <v>18</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>18</v>
@@ -7237,10 +7256,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7263,19 +7282,17 @@
         <v>90</v>
       </c>
       <c r="K48" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="L48" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="M48" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="L48" t="s" s="2">
+      <c r="N48" s="2"/>
+      <c r="O48" t="s" s="2">
         <v>291</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>292</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>294</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>18</v>
@@ -7324,7 +7341,7 @@
         <v>18</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>77</v>
@@ -7333,7 +7350,7 @@
         <v>89</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>18</v>
+        <v>285</v>
       </c>
       <c r="AJ48" t="s" s="2">
         <v>101</v>
@@ -7345,7 +7362,7 @@
         <v>18</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>18</v>
@@ -7356,10 +7373,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7382,19 +7399,19 @@
         <v>90</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>267</v>
+        <v>296</v>
       </c>
       <c r="L49" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="M49" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="N49" t="s" s="2">
         <v>299</v>
       </c>
-      <c r="M49" t="s" s="2">
+      <c r="O49" t="s" s="2">
         <v>300</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>302</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>18</v>
@@ -7443,7 +7460,7 @@
         <v>18</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>77</v>
@@ -7464,7 +7481,7 @@
         <v>18</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>18</v>
@@ -7475,10 +7492,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7501,16 +7518,20 @@
         <v>90</v>
       </c>
       <c r="K50" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="L50" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="M50" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="N50" t="s" s="2">
         <v>307</v>
       </c>
-      <c r="L50" t="s" s="2">
+      <c r="O50" t="s" s="2">
         <v>308</v>
       </c>
-      <c r="M50" t="s" s="2">
-        <v>309</v>
-      </c>
-      <c r="N50" s="2"/>
-      <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>18</v>
       </c>
@@ -7558,7 +7579,7 @@
         <v>18</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>77</v>
@@ -7579,7 +7600,7 @@
         <v>18</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>134</v>
+        <v>310</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>18</v>
@@ -7590,10 +7611,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>330</v>
+        <v>312</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7613,16 +7634,16 @@
         <v>18</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>235</v>
+        <v>313</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>331</v>
+        <v>314</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>332</v>
+        <v>315</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7649,13 +7670,13 @@
         <v>18</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>208</v>
+        <v>18</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>333</v>
+        <v>18</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>334</v>
+        <v>18</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>18</v>
@@ -7673,7 +7694,7 @@
         <v>18</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>330</v>
+        <v>316</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>77</v>
@@ -7688,27 +7709,27 @@
         <v>101</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>335</v>
+        <v>18</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>213</v>
+        <v>18</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>336</v>
+        <v>134</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>215</v>
+        <v>18</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>337</v>
+        <v>18</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7719,7 +7740,7 @@
         <v>77</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>18</v>
@@ -7731,13 +7752,13 @@
         <v>18</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>339</v>
+        <v>241</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -7764,13 +7785,13 @@
         <v>18</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>18</v>
+        <v>214</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>18</v>
+        <v>339</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>18</v>
+        <v>340</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>18</v>
@@ -7788,13 +7809,13 @@
         <v>18</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>18</v>
@@ -7803,27 +7824,27 @@
         <v>101</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>336</v>
+        <v>342</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>18</v>
+        <v>343</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7834,7 +7855,7 @@
         <v>77</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>18</v>
@@ -7846,18 +7867,16 @@
         <v>18</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="N53" s="2"/>
-      <c r="O53" t="s" s="2">
-        <v>346</v>
-      </c>
+      <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>18</v>
       </c>
@@ -7905,13 +7924,13 @@
         <v>18</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>18</v>
@@ -7920,16 +7939,16 @@
         <v>101</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>348</v>
+        <v>219</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>349</v>
+        <v>342</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>350</v>
+        <v>221</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>18</v>
@@ -7937,10 +7956,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7963,16 +7982,18 @@
         <v>18</v>
       </c>
       <c r="K54" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="L54" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="M54" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="N54" s="2"/>
+      <c r="O54" t="s" s="2">
         <v>352</v>
       </c>
-      <c r="L54" t="s" s="2">
-        <v>353</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>354</v>
-      </c>
-      <c r="N54" s="2"/>
-      <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>18</v>
       </c>
@@ -8020,7 +8041,7 @@
         <v>18</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>77</v>
@@ -8035,27 +8056,27 @@
         <v>101</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>335</v>
+        <v>353</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>213</v>
+        <v>354</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>336</v>
+        <v>355</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>215</v>
+        <v>356</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>18</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8063,35 +8084,31 @@
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="H55" t="s" s="2">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="I55" t="s" s="2">
         <v>18</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>359</v>
-      </c>
-      <c r="O55" t="s" s="2">
         <v>360</v>
       </c>
+      <c r="N55" s="2"/>
+      <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>18</v>
       </c>
@@ -8139,42 +8156,42 @@
         <v>18</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="AG55" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ55" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK55" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="AL55" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="AM55" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="AN55" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="AO55" t="s" s="2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s" s="2">
         <v>361</v>
       </c>
-      <c r="AK55" t="s" s="2">
-        <v>362</v>
-      </c>
-      <c r="AL55" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="AM55" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="AN55" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="AO55" t="s" s="2">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="56" hidden="true">
-      <c r="A56" t="s" s="2">
-        <v>367</v>
-      </c>
       <c r="B56" t="s" s="2">
-        <v>367</v>
+        <v>361</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8182,31 +8199,35 @@
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="H56" t="s" s="2">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="I56" t="s" s="2">
         <v>18</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>267</v>
+        <v>362</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>222</v>
+        <v>363</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="N56" s="2"/>
-      <c r="O56" s="2"/>
+        <v>364</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="O56" t="s" s="2">
+        <v>366</v>
+      </c>
       <c r="P56" t="s" s="2">
         <v>18</v>
       </c>
@@ -8254,53 +8275,53 @@
         <v>18</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>224</v>
+        <v>361</v>
       </c>
       <c r="AG56" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>225</v>
+        <v>18</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>18</v>
+        <v>367</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>18</v>
+        <v>368</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>18</v>
+        <v>369</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>226</v>
+        <v>370</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>18</v>
+        <v>371</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>18</v>
+        <v>372</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>154</v>
+        <v>18</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>18</v>
@@ -8312,17 +8333,15 @@
         <v>18</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>136</v>
+        <v>273</v>
       </c>
       <c r="L57" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="M57" t="s" s="2">
         <v>229</v>
       </c>
-      <c r="M57" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>157</v>
-      </c>
+      <c r="N57" s="2"/>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>18</v>
@@ -8371,28 +8390,28 @@
         <v>18</v>
       </c>
       <c r="AF57" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="AG57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH57" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI57" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="AJ57" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AK57" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AL57" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AM57" t="s" s="2">
         <v>232</v>
-      </c>
-      <c r="AG57" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH57" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI57" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AJ57" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="AK57" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AL57" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AM57" t="s" s="2">
-        <v>226</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>18</v>
@@ -8403,14 +8422,14 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>370</v>
+        <v>159</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -8423,26 +8442,24 @@
         <v>18</v>
       </c>
       <c r="I58" t="s" s="2">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="K58" t="s" s="2">
         <v>136</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>371</v>
+        <v>235</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>372</v>
+        <v>236</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="O58" t="s" s="2">
-        <v>158</v>
-      </c>
+        <v>162</v>
+      </c>
+      <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>18</v>
       </c>
@@ -8490,7 +8507,7 @@
         <v>18</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>373</v>
+        <v>238</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>77</v>
@@ -8511,7 +8528,7 @@
         <v>18</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>134</v>
+        <v>232</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>18</v>
@@ -8522,45 +8539,45 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>18</v>
+        <v>376</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>18</v>
       </c>
       <c r="I59" t="s" s="2">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="J59" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>235</v>
+        <v>136</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>377</v>
+        <v>162</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>378</v>
+        <v>163</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>18</v>
@@ -8585,66 +8602,66 @@
         <v>18</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>208</v>
+        <v>18</v>
       </c>
       <c r="Y59" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Z59" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AA59" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AB59" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AC59" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AD59" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AE59" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AF59" t="s" s="2">
         <v>379</v>
       </c>
-      <c r="Z59" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="AA59" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AB59" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AC59" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AD59" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AE59" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AF59" t="s" s="2">
-        <v>374</v>
-      </c>
       <c r="AG59" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>101</v>
+        <v>142</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>381</v>
+        <v>18</v>
       </c>
       <c r="AL59" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>382</v>
+        <v>134</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>383</v>
+        <v>18</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>384</v>
+        <v>18</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8655,7 +8672,7 @@
         <v>77</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>18</v>
@@ -8664,22 +8681,22 @@
         <v>18</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>386</v>
+        <v>381</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>18</v>
@@ -8704,13 +8721,13 @@
         <v>18</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>18</v>
@@ -8728,13 +8745,13 @@
         <v>18</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>18</v>
@@ -8743,27 +8760,27 @@
         <v>101</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>18</v>
+        <v>387</v>
       </c>
       <c r="AL60" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>18</v>
+        <v>389</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>393</v>
+        <v>390</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8771,10 +8788,10 @@
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>18</v>
@@ -8783,19 +8800,23 @@
         <v>18</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="K61" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="L61" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="M61" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="O61" t="s" s="2">
         <v>395</v>
       </c>
-      <c r="L61" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="M61" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="N61" s="2"/>
-      <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>18</v>
       </c>
@@ -8819,13 +8840,13 @@
         <v>18</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>18</v>
+        <v>214</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>18</v>
+        <v>396</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>18</v>
+        <v>397</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>18</v>
@@ -8843,42 +8864,42 @@
         <v>18</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="AG61" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>398</v>
+        <v>18</v>
       </c>
       <c r="AJ61" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK61" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AL61" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AM61" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="AN61" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AO61" t="s" s="2">
         <v>399</v>
-      </c>
-      <c r="AL61" t="s" s="2">
-        <v>400</v>
-      </c>
-      <c r="AM61" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="AN61" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AO61" t="s" s="2">
-        <v>18</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8886,7 +8907,7 @@
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="G62" t="s" s="2">
         <v>89</v>
@@ -8898,16 +8919,16 @@
         <v>18</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="K62" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="L62" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="M62" t="s" s="2">
         <v>403</v>
-      </c>
-      <c r="L62" t="s" s="2">
-        <v>404</v>
-      </c>
-      <c r="M62" t="s" s="2">
-        <v>405</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -8958,28 +8979,28 @@
         <v>18</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="AG62" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="AH62" t="s" s="2">
         <v>89</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>398</v>
+        <v>404</v>
       </c>
       <c r="AJ62" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>18</v>
+        <v>405</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>18</v>
+        <v>406</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>18</v>
@@ -8988,12 +9009,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9001,28 +9022,28 @@
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="H63" t="s" s="2">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="I63" t="s" s="2">
         <v>18</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>356</v>
+        <v>409</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -9073,16 +9094,16 @@
         <v>18</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>18</v>
+        <v>404</v>
       </c>
       <c r="AJ63" t="s" s="2">
         <v>101</v>
@@ -9094,16 +9115,16 @@
         <v>18</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>411</v>
+        <v>18</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>412</v>
+        <v>18</v>
       </c>
     </row>
-    <row r="64" hidden="true">
+    <row r="64">
       <c r="A64" t="s" s="2">
         <v>413</v>
       </c>
@@ -9116,28 +9137,28 @@
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="H64" t="s" s="2">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="I64" t="s" s="2">
         <v>18</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>267</v>
+        <v>362</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>222</v>
+        <v>414</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>223</v>
+        <v>415</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -9188,19 +9209,19 @@
         <v>18</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>224</v>
+        <v>413</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AI64" t="s" s="2">
-        <v>225</v>
+        <v>18</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>18</v>
+        <v>101</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>18</v>
@@ -9209,32 +9230,32 @@
         <v>18</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>226</v>
+        <v>416</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>18</v>
+        <v>417</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>18</v>
+        <v>418</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>154</v>
+        <v>18</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>18</v>
@@ -9246,17 +9267,15 @@
         <v>18</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>136</v>
+        <v>273</v>
       </c>
       <c r="L65" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="M65" t="s" s="2">
         <v>229</v>
       </c>
-      <c r="M65" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>157</v>
-      </c>
+      <c r="N65" s="2"/>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>18</v>
@@ -9305,28 +9324,28 @@
         <v>18</v>
       </c>
       <c r="AF65" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="AG65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH65" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI65" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="AJ65" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AK65" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AL65" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AM65" t="s" s="2">
         <v>232</v>
-      </c>
-      <c r="AG65" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH65" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI65" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AJ65" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="AK65" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AL65" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AM65" t="s" s="2">
-        <v>226</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>18</v>
@@ -9337,14 +9356,14 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>370</v>
+        <v>159</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
@@ -9357,26 +9376,24 @@
         <v>18</v>
       </c>
       <c r="I66" t="s" s="2">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="K66" t="s" s="2">
         <v>136</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>371</v>
+        <v>235</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>372</v>
+        <v>236</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="O66" t="s" s="2">
-        <v>158</v>
-      </c>
+        <v>162</v>
+      </c>
+      <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>18</v>
       </c>
@@ -9424,7 +9441,7 @@
         <v>18</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>373</v>
+        <v>238</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>77</v>
@@ -9445,7 +9462,7 @@
         <v>18</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>134</v>
+        <v>232</v>
       </c>
       <c r="AN66" t="s" s="2">
         <v>18</v>
@@ -9456,42 +9473,46 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>18</v>
+        <v>376</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>18</v>
       </c>
       <c r="I67" t="s" s="2">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="J67" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>109</v>
+        <v>136</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>417</v>
+        <v>377</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="N67" s="2"/>
-      <c r="O67" s="2"/>
+        <v>378</v>
+      </c>
+      <c r="N67" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="O67" t="s" s="2">
+        <v>163</v>
+      </c>
       <c r="P67" t="s" s="2">
         <v>18</v>
       </c>
@@ -9500,7 +9521,7 @@
         <v>18</v>
       </c>
       <c r="S67" t="s" s="2">
-        <v>419</v>
+        <v>18</v>
       </c>
       <c r="T67" t="s" s="2">
         <v>18</v>
@@ -9515,13 +9536,13 @@
         <v>18</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>113</v>
+        <v>18</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>420</v>
+        <v>18</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>421</v>
+        <v>18</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>18</v>
@@ -9539,19 +9560,19 @@
         <v>18</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>416</v>
+        <v>379</v>
       </c>
       <c r="AG67" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>101</v>
+        <v>142</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>18</v>
@@ -9560,21 +9581,21 @@
         <v>18</v>
       </c>
       <c r="AM67" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="AN67" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AO67" t="s" s="2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="68" hidden="true">
+      <c r="A68" t="s" s="2">
         <v>422</v>
       </c>
-      <c r="AN67" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="AO67" t="s" s="2">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="s" s="2">
-        <v>425</v>
-      </c>
       <c r="B68" t="s" s="2">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9588,7 +9609,7 @@
         <v>89</v>
       </c>
       <c r="H68" t="s" s="2">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="I68" t="s" s="2">
         <v>18</v>
@@ -9597,17 +9618,15 @@
         <v>90</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>426</v>
+        <v>109</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>429</v>
-      </c>
+        <v>424</v>
+      </c>
+      <c r="N68" s="2"/>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>18</v>
@@ -9617,7 +9636,7 @@
         <v>18</v>
       </c>
       <c r="S68" t="s" s="2">
-        <v>18</v>
+        <v>425</v>
       </c>
       <c r="T68" t="s" s="2">
         <v>18</v>
@@ -9632,13 +9651,13 @@
         <v>18</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>18</v>
+        <v>113</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>18</v>
+        <v>426</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>18</v>
+        <v>427</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>18</v>
@@ -9656,7 +9675,7 @@
         <v>18</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>89</v>
@@ -9677,13 +9696,13 @@
         <v>18</v>
       </c>
       <c r="AM68" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="AN68" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="AO68" t="s" s="2">
         <v>430</v>
-      </c>
-      <c r="AN68" t="s" s="2">
-        <v>350</v>
-      </c>
-      <c r="AO68" t="s" s="2">
-        <v>168</v>
       </c>
     </row>
     <row r="69" hidden="true">
@@ -9699,10 +9718,10 @@
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>18</v>
@@ -9711,19 +9730,19 @@
         <v>18</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>79</v>
+        <v>432</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -9776,10 +9795,10 @@
         <v>431</v>
       </c>
       <c r="AG69" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>18</v>
@@ -9794,13 +9813,13 @@
         <v>18</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>18</v>
+        <v>356</v>
       </c>
       <c r="AO69" t="s" s="2">
-        <v>436</v>
+        <v>173</v>
       </c>
     </row>
     <row r="70" hidden="true">
@@ -9831,15 +9850,17 @@
         <v>18</v>
       </c>
       <c r="K70" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="L70" t="s" s="2">
         <v>438</v>
       </c>
-      <c r="L70" t="s" s="2">
+      <c r="M70" t="s" s="2">
         <v>439</v>
       </c>
-      <c r="M70" t="s" s="2">
+      <c r="N70" t="s" s="2">
         <v>440</v>
       </c>
-      <c r="N70" s="2"/>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>18</v>
@@ -9915,11 +9936,126 @@
         <v>18</v>
       </c>
       <c r="AO70" t="s" s="2">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="71" hidden="true">
+      <c r="A71" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="B71" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="C71" s="2"/>
+      <c r="D71" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="E71" s="2"/>
+      <c r="F71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H71" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I71" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J71" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="K71" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="L71" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="M71" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="N71" s="2"/>
+      <c r="O71" s="2"/>
+      <c r="P71" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Q71" s="2"/>
+      <c r="R71" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="S71" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="T71" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="U71" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="V71" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="W71" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="X71" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Y71" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Z71" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AA71" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AB71" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AC71" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AD71" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AE71" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AF71" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="AG71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI71" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AJ71" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK71" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AL71" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AM71" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="AN71" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AO71" t="s" s="2">
         <v>18</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO70">
+  <autoFilter ref="A1:AO71">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -9929,7 +10065,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI69">
+  <conditionalFormatting sqref="A2:AI70">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/r5-aist-trustworthyai-main/StructureDefinition-eu-ai-provenance.xlsx
+++ b/r5-aist-trustworthyai-main/StructureDefinition-eu-ai-provenance.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$71</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$75</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2655" uniqueCount="448">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2803" uniqueCount="467">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T12:04:51+00:00</t>
+    <t>2026-07-31T11:07:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -474,10 +474,10 @@
 </t>
   </si>
   <si>
-    <t>Primary vs. Secondary Use Category</t>
-  </si>
-  <si>
-    <t>Categorizes the data processing as Primary Care or Secondary Use according to the EHDS.</t>
+    <t>Primary or secondary use category</t>
+  </si>
+  <si>
+    <t>Classifies the documented use of electronic health data as primary use or secondary use in the EHDS context.</t>
   </si>
   <si>
     <t>Provenance.extension:secondaryUsePurpose</t>
@@ -490,10 +490,10 @@
 </t>
   </si>
   <si>
-    <t>EHDS Secondary Use Purpose</t>
-  </si>
-  <si>
-    <t>Documents the permitted purpose for secondary use of electronic health data under the EHDS.</t>
+    <t>Purpose of secondary use, where applicable</t>
+  </si>
+  <si>
+    <t>Records the documented purpose for secondary use of electronic health data in the EHDS context.</t>
   </si>
   <si>
     <t>Provenance.extension:dataPermit</t>
@@ -506,10 +506,10 @@
 </t>
   </si>
   <si>
-    <t>Reference to the EHDS Data Access Permit</t>
-  </si>
-  <si>
-    <t>The unique ID of the Health Data Access Body permit (required if secondary use).</t>
+    <t>EHDS data permit, where applicable</t>
+  </si>
+  <si>
+    <t>Records the identifier of an EHDS data permit associated with the documented secondary use, where applicable.</t>
   </si>
   <si>
     <t>Provenance.modifierExtension</t>
@@ -570,7 +570,7 @@
 </t>
   </si>
   <si>
-    <t>Exact execution period (Start/End) of the AI model</t>
+    <t>Execution period of the AI processing activity</t>
   </si>
   <si>
     <t>The period during which the activity occurred.</t>
@@ -589,6 +589,87 @@
   </si>
   <si>
     <t>Activity.startTime &amp; Activity.endTime</t>
+  </si>
+  <si>
+    <t>Provenance.occurred[x].id</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>Provenance.occurred[x].extension</t>
+  </si>
+  <si>
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and managable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>Provenance.occurred[x].start</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dateTime
+</t>
+  </si>
+  <si>
+    <t>Start of the AI processing activity</t>
+  </si>
+  <si>
+    <t>The start of the period. The boundary is inclusive.</t>
+  </si>
+  <si>
+    <t>If the low element is missing, the meaning is that the low boundary is not known.</t>
+  </si>
+  <si>
+    <t>Period.start</t>
+  </si>
+  <si>
+    <t xml:space="preserve">per-1
+</t>
+  </si>
+  <si>
+    <t>./low</t>
+  </si>
+  <si>
+    <t>Provenance.occurred[x].end</t>
+  </si>
+  <si>
+    <t>End of the AI processing activity</t>
+  </si>
+  <si>
+    <t>The end of the period. If the end of the period is missing, it means no end was known or planned at the time the instance was created. The start may be in the past, and the end date in the future, which means that period is expected/planned to end at that time.</t>
+  </si>
+  <si>
+    <t>The end value includes any matching date/time. i.e. 2012-02-03T10:00:00 is in a period that has an end value of 2012-02-03.</t>
+  </si>
+  <si>
+    <t>If the end of the period is missing, it means that the period is ongoing</t>
+  </si>
+  <si>
+    <t>Period.end</t>
+  </si>
+  <si>
+    <t>./high</t>
   </si>
   <si>
     <t>Provenance.recorded</t>
@@ -598,7 +679,7 @@
 </t>
   </si>
   <si>
-    <t>When the activity was recorded / updated</t>
+    <t>Time when the provenance record was created</t>
   </si>
   <si>
     <t>The instant of time at which the activity was recorded.</t>
@@ -716,56 +797,31 @@
     <t>AuditEvent.purposeOfEvent</t>
   </si>
   <si>
-    <t>Provenance.authorization:gdprBasis</t>
-  </si>
-  <si>
-    <t>gdprBasis</t>
+    <t>Provenance.authorization:gdprArt6Basis</t>
+  </si>
+  <si>
+    <t>gdprArt6Basis</t>
+  </si>
+  <si>
+    <t>Legal basis under GDPR Article 6</t>
   </si>
   <si>
     <t>http://example.org/fhir/eu-ai-transparency/ValueSet/gdpr-art6-legal-basis-vs</t>
   </si>
   <si>
-    <t>Provenance.authorization:gdprBasis.id</t>
+    <t>Provenance.authorization:gdprArt6Basis.id</t>
   </si>
   <si>
     <t>Provenance.authorization.id</t>
   </si>
   <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ele-1
-</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
-    <t>Provenance.authorization:gdprBasis.extension</t>
+    <t>Provenance.authorization:gdprArt6Basis.extension</t>
   </si>
   <si>
     <t>Provenance.authorization.extension</t>
   </si>
   <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and managable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
-  </si>
-  <si>
-    <t>Provenance.authorization:gdprBasis.concept</t>
+    <t>Provenance.authorization:gdprArt6Basis.concept</t>
   </si>
   <si>
     <t>Provenance.authorization.concept</t>
@@ -784,19 +840,19 @@
     <t>CodeableReference.concept</t>
   </si>
   <si>
-    <t>Provenance.authorization:gdprBasis.concept.id</t>
+    <t>Provenance.authorization:gdprArt6Basis.concept.id</t>
   </si>
   <si>
     <t>Provenance.authorization.concept.id</t>
   </si>
   <si>
-    <t>Provenance.authorization:gdprBasis.concept.extension</t>
+    <t>Provenance.authorization:gdprArt6Basis.concept.extension</t>
   </si>
   <si>
     <t>Provenance.authorization.concept.extension</t>
   </si>
   <si>
-    <t>Provenance.authorization:gdprBasis.concept.coding</t>
+    <t>Provenance.authorization:gdprArt6Basis.concept.coding</t>
   </si>
   <si>
     <t>Provenance.authorization.concept.coding</t>
@@ -824,19 +880,19 @@
     <t>union(., ./translation)</t>
   </si>
   <si>
-    <t>Provenance.authorization:gdprBasis.concept.coding.id</t>
+    <t>Provenance.authorization:gdprArt6Basis.concept.coding.id</t>
   </si>
   <si>
     <t>Provenance.authorization.concept.coding.id</t>
   </si>
   <si>
-    <t>Provenance.authorization:gdprBasis.concept.coding.extension</t>
+    <t>Provenance.authorization:gdprArt6Basis.concept.coding.extension</t>
   </si>
   <si>
     <t>Provenance.authorization.concept.coding.extension</t>
   </si>
   <si>
-    <t>Provenance.authorization:gdprBasis.concept.coding.system</t>
+    <t>Provenance.authorization:gdprArt6Basis.concept.coding.system</t>
   </si>
   <si>
     <t>Provenance.authorization.concept.coding.system</t>
@@ -863,7 +919,7 @@
     <t>./codeSystem</t>
   </si>
   <si>
-    <t>Provenance.authorization:gdprBasis.concept.coding.version</t>
+    <t>Provenance.authorization:gdprArt6Basis.concept.coding.version</t>
   </si>
   <si>
     <t>Provenance.authorization.concept.coding.version</t>
@@ -888,7 +944,7 @@
     <t>./codeSystemVersion</t>
   </si>
   <si>
-    <t>Provenance.authorization:gdprBasis.concept.coding.code</t>
+    <t>Provenance.authorization:gdprArt6Basis.concept.coding.code</t>
   </si>
   <si>
     <t>Provenance.authorization.concept.coding.code</t>
@@ -913,7 +969,7 @@
     <t>./code</t>
   </si>
   <si>
-    <t>Provenance.authorization:gdprBasis.concept.coding.display</t>
+    <t>Provenance.authorization:gdprArt6Basis.concept.coding.display</t>
   </si>
   <si>
     <t>Provenance.authorization.concept.coding.display</t>
@@ -934,7 +990,7 @@
     <t>CV.displayName</t>
   </si>
   <si>
-    <t>Provenance.authorization:gdprBasis.concept.coding.userSelected</t>
+    <t>Provenance.authorization:gdprArt6Basis.concept.coding.userSelected</t>
   </si>
   <si>
     <t>Provenance.authorization.concept.coding.userSelected</t>
@@ -962,7 +1018,7 @@
     <t>CD.codingRationale</t>
   </si>
   <si>
-    <t>Provenance.authorization:gdprBasis.concept.text</t>
+    <t>Provenance.authorization:gdprArt6Basis.concept.text</t>
   </si>
   <si>
     <t>Provenance.authorization.concept.text</t>
@@ -986,7 +1042,7 @@
     <t>./originalText[mediaType/code="text/plain"]/data</t>
   </si>
   <si>
-    <t>Provenance.authorization:gdprBasis.reference</t>
+    <t>Provenance.authorization:gdprArt6Basis.reference</t>
   </si>
   <si>
     <t>Provenance.authorization.reference</t>
@@ -1005,61 +1061,64 @@
     <t>CodeableReference.reference</t>
   </si>
   <si>
-    <t>Provenance.authorization:gdprException</t>
-  </si>
-  <si>
-    <t>gdprException</t>
-  </si>
-  <si>
-    <t>http://example.org/fhir/eu-ai-transparency/ValueSet/gdpr-art9-exception-vs</t>
-  </si>
-  <si>
-    <t>Provenance.authorization:gdprException.id</t>
-  </si>
-  <si>
-    <t>Provenance.authorization:gdprException.extension</t>
-  </si>
-  <si>
-    <t>Provenance.authorization:gdprException.concept</t>
-  </si>
-  <si>
-    <t>Provenance.authorization:gdprException.concept.id</t>
-  </si>
-  <si>
-    <t>Provenance.authorization:gdprException.concept.extension</t>
-  </si>
-  <si>
-    <t>Provenance.authorization:gdprException.concept.coding</t>
-  </si>
-  <si>
-    <t>Provenance.authorization:gdprException.concept.coding.id</t>
-  </si>
-  <si>
-    <t>Provenance.authorization:gdprException.concept.coding.extension</t>
-  </si>
-  <si>
-    <t>Provenance.authorization:gdprException.concept.coding.system</t>
+    <t>Provenance.authorization:gdprArt9Condition</t>
+  </si>
+  <si>
+    <t>gdprArt9Condition</t>
+  </si>
+  <si>
+    <t>Condition under GDPR Article 9 for processing health data</t>
+  </si>
+  <si>
+    <t>http://example.org/fhir/eu-ai-transparency/ValueSet/gdpr-art9-condition-vs</t>
+  </si>
+  <si>
+    <t>Provenance.authorization:gdprArt9Condition.id</t>
+  </si>
+  <si>
+    <t>Provenance.authorization:gdprArt9Condition.extension</t>
+  </si>
+  <si>
+    <t>Provenance.authorization:gdprArt9Condition.concept</t>
+  </si>
+  <si>
+    <t>Provenance.authorization:gdprArt9Condition.concept.id</t>
+  </si>
+  <si>
+    <t>Provenance.authorization:gdprArt9Condition.concept.extension</t>
+  </si>
+  <si>
+    <t>Provenance.authorization:gdprArt9Condition.concept.coding</t>
+  </si>
+  <si>
+    <t>Provenance.authorization:gdprArt9Condition.concept.coding.id</t>
+  </si>
+  <si>
+    <t>Provenance.authorization:gdprArt9Condition.concept.coding.extension</t>
+  </si>
+  <si>
+    <t>Provenance.authorization:gdprArt9Condition.concept.coding.system</t>
   </si>
   <si>
     <t>http://example.org/fhir/eu-ai-transparency/CodeSystem/gdpr-art9-codesystem</t>
   </si>
   <si>
-    <t>Provenance.authorization:gdprException.concept.coding.version</t>
-  </si>
-  <si>
-    <t>Provenance.authorization:gdprException.concept.coding.code</t>
-  </si>
-  <si>
-    <t>Provenance.authorization:gdprException.concept.coding.display</t>
-  </si>
-  <si>
-    <t>Provenance.authorization:gdprException.concept.coding.userSelected</t>
-  </si>
-  <si>
-    <t>Provenance.authorization:gdprException.concept.text</t>
-  </si>
-  <si>
-    <t>Provenance.authorization:gdprException.reference</t>
+    <t>Provenance.authorization:gdprArt9Condition.concept.coding.version</t>
+  </si>
+  <si>
+    <t>Provenance.authorization:gdprArt9Condition.concept.coding.code</t>
+  </si>
+  <si>
+    <t>Provenance.authorization:gdprArt9Condition.concept.coding.display</t>
+  </si>
+  <si>
+    <t>Provenance.authorization:gdprArt9Condition.concept.coding.userSelected</t>
+  </si>
+  <si>
+    <t>Provenance.authorization:gdprArt9Condition.concept.text</t>
+  </si>
+  <si>
+    <t>Provenance.authorization:gdprArt9Condition.reference</t>
   </si>
   <si>
     <t>Provenance.activity</t>
@@ -1268,7 +1327,7 @@
 </t>
   </si>
   <si>
-    <t>Link to the AI Device that executed the action</t>
+    <t>AI system that performed the processing activity</t>
   </si>
   <si>
     <t>Indicates who or what performed in the event.</t>
@@ -1716,10 +1775,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO71"/>
+  <dimension ref="A1:AO75"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="56.2421875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="59.31640625" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="44.3125" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="18.3125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
@@ -3545,20 +3604,18 @@
         <v>18</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="K16" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="L16" t="s" s="2">
         <v>184</v>
       </c>
-      <c r="L16" t="s" s="2">
+      <c r="M16" t="s" s="2">
         <v>185</v>
       </c>
-      <c r="M16" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="N16" t="s" s="2">
-        <v>187</v>
-      </c>
+      <c r="N16" s="2"/>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
         <v>18</v>
@@ -3607,7 +3664,7 @@
         <v>18</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>77</v>
@@ -3616,37 +3673,37 @@
         <v>89</v>
       </c>
       <c r="AI16" t="s" s="2">
-        <v>18</v>
+        <v>187</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>101</v>
+        <v>18</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AL16" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AM16" t="s" s="2">
         <v>188</v>
       </c>
-      <c r="AM16" t="s" s="2">
-        <v>189</v>
-      </c>
       <c r="AN16" t="s" s="2">
-        <v>190</v>
+        <v>18</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>191</v>
+        <v>18</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>18</v>
+        <v>159</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -3665,16 +3722,16 @@
         <v>18</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>103</v>
+        <v>136</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>195</v>
+        <v>162</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3712,19 +3769,19 @@
         <v>18</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>18</v>
+        <v>139</v>
       </c>
       <c r="AC17" t="s" s="2">
-        <v>18</v>
+        <v>192</v>
       </c>
       <c r="AD17" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>18</v>
+        <v>140</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>77</v>
@@ -3736,7 +3793,7 @@
         <v>18</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>101</v>
+        <v>142</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>18</v>
@@ -3745,21 +3802,21 @@
         <v>18</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="AN17" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>197</v>
+        <v>18</v>
       </c>
     </row>
-    <row r="18" hidden="true">
+    <row r="18">
       <c r="A18" t="s" s="2">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3767,30 +3824,32 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="G18" t="s" s="2">
         <v>89</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="I18" t="s" s="2">
         <v>18</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>201</v>
-      </c>
-      <c r="N18" s="2"/>
+        <v>197</v>
+      </c>
+      <c r="N18" t="s" s="2">
+        <v>198</v>
+      </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>18</v>
@@ -3839,7 +3898,7 @@
         <v>18</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>77</v>
@@ -3848,44 +3907,44 @@
         <v>89</v>
       </c>
       <c r="AI18" t="s" s="2">
-        <v>18</v>
+        <v>200</v>
       </c>
       <c r="AJ18" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK18" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AL18" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AM18" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="AN18" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AO18" t="s" s="2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="2">
         <v>202</v>
       </c>
-      <c r="AL18" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="AM18" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="AN18" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="AO18" t="s" s="2">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="19" hidden="true">
-      <c r="A19" t="s" s="2">
-        <v>207</v>
-      </c>
       <c r="B19" t="s" s="2">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>208</v>
+        <v>18</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>209</v>
+        <v>89</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>90</v>
@@ -3894,25 +3953,27 @@
         <v>18</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>210</v>
+        <v>195</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="N19" s="2"/>
-      <c r="O19" t="s" s="2">
-        <v>213</v>
-      </c>
+        <v>204</v>
+      </c>
+      <c r="N19" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>18</v>
       </c>
-      <c r="Q19" s="2"/>
+      <c r="Q19" t="s" s="2">
+        <v>206</v>
+      </c>
       <c r="R19" t="s" s="2">
         <v>18</v>
       </c>
@@ -3932,26 +3993,28 @@
         <v>18</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>214</v>
+        <v>18</v>
       </c>
       <c r="Y19" t="s" s="2">
-        <v>215</v>
+        <v>18</v>
       </c>
       <c r="Z19" t="s" s="2">
-        <v>216</v>
+        <v>18</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="AC19" s="2"/>
+        <v>18</v>
+      </c>
+      <c r="AC19" t="s" s="2">
+        <v>18</v>
+      </c>
       <c r="AD19" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>140</v>
+        <v>18</v>
       </c>
       <c r="AF19" t="s" s="2">
         <v>207</v>
@@ -3960,42 +4023,40 @@
         <v>77</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>18</v>
+        <v>200</v>
       </c>
       <c r="AJ19" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>218</v>
+        <v>18</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>219</v>
+        <v>18</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>220</v>
+        <v>208</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>221</v>
+        <v>18</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>222</v>
+        <v>18</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>223</v>
+        <v>209</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="C20" t="s" s="2">
-        <v>224</v>
-      </c>
+        <v>209</v>
+      </c>
+      <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>208</v>
+        <v>18</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -4011,7 +4072,7 @@
         <v>18</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="K20" t="s" s="2">
         <v>210</v>
@@ -4022,10 +4083,10 @@
       <c r="M20" t="s" s="2">
         <v>212</v>
       </c>
-      <c r="N20" s="2"/>
-      <c r="O20" t="s" s="2">
+      <c r="N20" t="s" s="2">
         <v>213</v>
       </c>
+      <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>18</v>
       </c>
@@ -4049,11 +4110,13 @@
         <v>18</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="Y20" s="2"/>
+        <v>18</v>
+      </c>
+      <c r="Y20" t="s" s="2">
+        <v>18</v>
+      </c>
       <c r="Z20" t="s" s="2">
-        <v>225</v>
+        <v>18</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>18</v>
@@ -4071,13 +4134,13 @@
         <v>18</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>18</v>
@@ -4086,27 +4149,27 @@
         <v>101</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>218</v>
+        <v>18</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>222</v>
+        <v>217</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4117,7 +4180,7 @@
         <v>77</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>18</v>
@@ -4129,15 +4192,17 @@
         <v>18</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="N21" s="2"/>
+        <v>220</v>
+      </c>
+      <c r="N21" t="s" s="2">
+        <v>221</v>
+      </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>18</v>
@@ -4186,19 +4251,19 @@
         <v>18</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>230</v>
+        <v>218</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>231</v>
+        <v>18</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>18</v>
+        <v>101</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>18</v>
@@ -4207,32 +4272,32 @@
         <v>18</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>232</v>
+        <v>222</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>18</v>
+        <v>223</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>233</v>
+        <v>224</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>234</v>
+        <v>224</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>159</v>
+        <v>18</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>18</v>
@@ -4244,17 +4309,15 @@
         <v>18</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>136</v>
+        <v>225</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>235</v>
+        <v>226</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>162</v>
-      </c>
+        <v>227</v>
+      </c>
+      <c r="N22" s="2"/>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>18</v>
@@ -4291,86 +4354,88 @@
         <v>18</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>139</v>
+        <v>18</v>
       </c>
       <c r="AC22" t="s" s="2">
-        <v>237</v>
+        <v>18</v>
       </c>
       <c r="AD22" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>140</v>
+        <v>18</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>238</v>
+        <v>224</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>142</v>
+        <v>101</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>18</v>
+        <v>228</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>18</v>
+        <v>229</v>
       </c>
       <c r="AM22" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="AN22" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="AO22" t="s" s="2">
         <v>232</v>
-      </c>
-      <c r="AN22" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AO22" t="s" s="2">
-        <v>18</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>18</v>
+        <v>234</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>89</v>
+        <v>235</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>18</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="N23" s="2"/>
-      <c r="O23" s="2"/>
+      <c r="O23" t="s" s="2">
+        <v>239</v>
+      </c>
       <c r="P23" t="s" s="2">
         <v>18</v>
       </c>
@@ -4394,37 +4459,35 @@
         <v>18</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>18</v>
+        <v>240</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>18</v>
+        <v>241</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>18</v>
+        <v>242</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AC23" t="s" s="2">
-        <v>18</v>
-      </c>
+        <v>243</v>
+      </c>
+      <c r="AC23" s="2"/>
       <c r="AD23" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>18</v>
+        <v>140</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>244</v>
+        <v>233</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>18</v>
@@ -4433,41 +4496,43 @@
         <v>101</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>18</v>
+        <v>244</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>18</v>
+        <v>245</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>134</v>
+        <v>246</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>18</v>
+        <v>247</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>18</v>
+        <v>248</v>
       </c>
     </row>
-    <row r="24" hidden="true">
+    <row r="24">
       <c r="A24" t="s" s="2">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="C24" s="2"/>
+        <v>233</v>
+      </c>
+      <c r="C24" t="s" s="2">
+        <v>250</v>
+      </c>
       <c r="D24" t="s" s="2">
-        <v>18</v>
+        <v>234</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="G24" t="s" s="2">
         <v>89</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>18</v>
@@ -4476,16 +4541,18 @@
         <v>18</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>91</v>
+        <v>236</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>228</v>
+        <v>251</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>229</v>
+        <v>238</v>
       </c>
       <c r="N24" s="2"/>
-      <c r="O24" s="2"/>
+      <c r="O24" t="s" s="2">
+        <v>239</v>
+      </c>
       <c r="P24" t="s" s="2">
         <v>18</v>
       </c>
@@ -4509,13 +4576,11 @@
         <v>18</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="Y24" t="s" s="2">
-        <v>18</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="Y24" s="2"/>
       <c r="Z24" t="s" s="2">
-        <v>18</v>
+        <v>252</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>18</v>
@@ -4533,53 +4598,53 @@
         <v>18</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>231</v>
+        <v>18</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>18</v>
+        <v>101</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>18</v>
+        <v>244</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>18</v>
+        <v>245</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>232</v>
+        <v>246</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>18</v>
+        <v>247</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>18</v>
+        <v>248</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>159</v>
+        <v>18</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>18</v>
@@ -4591,17 +4656,15 @@
         <v>18</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>136</v>
+        <v>91</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>235</v>
+        <v>184</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>162</v>
-      </c>
+        <v>185</v>
+      </c>
+      <c r="N25" s="2"/>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>18</v>
@@ -4638,31 +4701,31 @@
         <v>18</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>139</v>
+        <v>18</v>
       </c>
       <c r="AC25" t="s" s="2">
-        <v>237</v>
+        <v>18</v>
       </c>
       <c r="AD25" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>140</v>
+        <v>18</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>238</v>
+        <v>186</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>18</v>
+        <v>187</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>142</v>
+        <v>18</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>18</v>
@@ -4671,7 +4734,7 @@
         <v>18</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>232</v>
+        <v>188</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>18</v>
@@ -4682,14 +4745,14 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>18</v>
+        <v>159</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -4705,23 +4768,21 @@
         <v>18</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>251</v>
+        <v>136</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>252</v>
+        <v>190</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>253</v>
+        <v>191</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>254</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>255</v>
-      </c>
+        <v>162</v>
+      </c>
+      <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>18</v>
       </c>
@@ -4757,19 +4818,19 @@
         <v>18</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>18</v>
+        <v>139</v>
       </c>
       <c r="AC26" t="s" s="2">
-        <v>18</v>
+        <v>192</v>
       </c>
       <c r="AD26" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>18</v>
+        <v>140</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>256</v>
+        <v>193</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>77</v>
@@ -4781,7 +4842,7 @@
         <v>18</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>101</v>
+        <v>142</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>18</v>
@@ -4790,7 +4851,7 @@
         <v>18</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>257</v>
+        <v>188</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>18</v>
@@ -4801,10 +4862,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="B27" t="s" s="2">
         <v>258</v>
-      </c>
-      <c r="B27" t="s" s="2">
-        <v>259</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4812,7 +4873,7 @@
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="G27" t="s" s="2">
         <v>89</v>
@@ -4824,16 +4885,16 @@
         <v>18</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>91</v>
+        <v>259</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>228</v>
+        <v>260</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>229</v>
+        <v>261</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -4884,7 +4945,7 @@
         <v>18</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>230</v>
+        <v>262</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>77</v>
@@ -4893,10 +4954,10 @@
         <v>89</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>231</v>
+        <v>18</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>18</v>
+        <v>101</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>18</v>
@@ -4905,7 +4966,7 @@
         <v>18</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>232</v>
+        <v>134</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>18</v>
@@ -4916,21 +4977,21 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>159</v>
+        <v>18</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>18</v>
@@ -4942,17 +5003,15 @@
         <v>18</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>136</v>
+        <v>91</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>235</v>
+        <v>184</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>162</v>
-      </c>
+        <v>185</v>
+      </c>
+      <c r="N28" s="2"/>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>18</v>
@@ -4989,31 +5048,31 @@
         <v>18</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>139</v>
+        <v>18</v>
       </c>
       <c r="AC28" t="s" s="2">
-        <v>237</v>
+        <v>18</v>
       </c>
       <c r="AD28" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>140</v>
+        <v>18</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>238</v>
+        <v>186</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>18</v>
+        <v>187</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>142</v>
+        <v>18</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>18</v>
@@ -5022,7 +5081,7 @@
         <v>18</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>232</v>
+        <v>188</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>18</v>
@@ -5033,21 +5092,21 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>18</v>
+        <v>159</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>18</v>
@@ -5056,23 +5115,21 @@
         <v>18</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>103</v>
+        <v>136</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>264</v>
+        <v>190</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>265</v>
+        <v>191</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="O29" t="s" s="2">
-        <v>267</v>
-      </c>
+        <v>162</v>
+      </c>
+      <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>18</v>
       </c>
@@ -5081,7 +5138,7 @@
         <v>18</v>
       </c>
       <c r="S29" t="s" s="2">
-        <v>268</v>
+        <v>18</v>
       </c>
       <c r="T29" t="s" s="2">
         <v>18</v>
@@ -5108,31 +5165,31 @@
         <v>18</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>18</v>
+        <v>139</v>
       </c>
       <c r="AC29" t="s" s="2">
-        <v>18</v>
+        <v>192</v>
       </c>
       <c r="AD29" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>18</v>
+        <v>140</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>269</v>
+        <v>193</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>101</v>
+        <v>142</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>18</v>
@@ -5141,7 +5198,7 @@
         <v>18</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>270</v>
+        <v>188</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>18</v>
@@ -5152,10 +5209,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5163,10 +5220,10 @@
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>18</v>
@@ -5178,18 +5235,20 @@
         <v>90</v>
       </c>
       <c r="K30" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="L30" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="M30" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="N30" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="O30" t="s" s="2">
         <v>273</v>
       </c>
-      <c r="L30" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="M30" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>276</v>
-      </c>
-      <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>18</v>
       </c>
@@ -5237,13 +5296,13 @@
         <v>18</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>18</v>
@@ -5258,7 +5317,7 @@
         <v>18</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>18</v>
@@ -5269,10 +5328,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5292,21 +5351,19 @@
         <v>18</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>109</v>
+        <v>91</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>281</v>
+        <v>184</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>282</v>
+        <v>185</v>
       </c>
       <c r="N31" s="2"/>
-      <c r="O31" t="s" s="2">
-        <v>283</v>
-      </c>
+      <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>18</v>
       </c>
@@ -5354,7 +5411,7 @@
         <v>18</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>284</v>
+        <v>186</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>77</v>
@@ -5363,10 +5420,10 @@
         <v>89</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>285</v>
+        <v>187</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>101</v>
+        <v>18</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>18</v>
@@ -5375,7 +5432,7 @@
         <v>18</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>286</v>
+        <v>188</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>18</v>
@@ -5386,21 +5443,21 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>287</v>
+        <v>278</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>288</v>
+        <v>279</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>18</v>
+        <v>159</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>18</v>
@@ -5409,21 +5466,21 @@
         <v>18</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>273</v>
+        <v>136</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>289</v>
+        <v>190</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>290</v>
-      </c>
-      <c r="N32" s="2"/>
-      <c r="O32" t="s" s="2">
-        <v>291</v>
-      </c>
+        <v>191</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>18</v>
       </c>
@@ -5459,31 +5516,31 @@
         <v>18</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>18</v>
+        <v>139</v>
       </c>
       <c r="AC32" t="s" s="2">
-        <v>18</v>
+        <v>192</v>
       </c>
       <c r="AD32" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>18</v>
+        <v>140</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>292</v>
+        <v>193</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>285</v>
+        <v>18</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>101</v>
+        <v>142</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>18</v>
@@ -5492,7 +5549,7 @@
         <v>18</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>293</v>
+        <v>188</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>18</v>
@@ -5503,10 +5560,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>294</v>
+        <v>280</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>295</v>
+        <v>281</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5514,7 +5571,7 @@
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="G33" t="s" s="2">
         <v>89</v>
@@ -5529,19 +5586,19 @@
         <v>90</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>296</v>
+        <v>103</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>297</v>
+        <v>282</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>298</v>
+        <v>283</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>299</v>
+        <v>284</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>300</v>
+        <v>285</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>18</v>
@@ -5551,7 +5608,7 @@
         <v>18</v>
       </c>
       <c r="S33" t="s" s="2">
-        <v>18</v>
+        <v>286</v>
       </c>
       <c r="T33" t="s" s="2">
         <v>18</v>
@@ -5590,7 +5647,7 @@
         <v>18</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>301</v>
+        <v>287</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>77</v>
@@ -5611,7 +5668,7 @@
         <v>18</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>302</v>
+        <v>288</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>18</v>
@@ -5622,10 +5679,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>303</v>
+        <v>289</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>304</v>
+        <v>290</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5648,20 +5705,18 @@
         <v>90</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>273</v>
+        <v>291</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>305</v>
+        <v>292</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>306</v>
+        <v>293</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>307</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>308</v>
-      </c>
+        <v>294</v>
+      </c>
+      <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>18</v>
       </c>
@@ -5709,7 +5764,7 @@
         <v>18</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>309</v>
+        <v>295</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>77</v>
@@ -5730,7 +5785,7 @@
         <v>18</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>310</v>
+        <v>296</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>18</v>
@@ -5741,10 +5796,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>311</v>
+        <v>297</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>312</v>
+        <v>298</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5767,16 +5822,18 @@
         <v>90</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>313</v>
+        <v>109</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>314</v>
+        <v>299</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>315</v>
+        <v>300</v>
       </c>
       <c r="N35" s="2"/>
-      <c r="O35" s="2"/>
+      <c r="O35" t="s" s="2">
+        <v>301</v>
+      </c>
       <c r="P35" t="s" s="2">
         <v>18</v>
       </c>
@@ -5824,7 +5881,7 @@
         <v>18</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>316</v>
+        <v>302</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>77</v>
@@ -5833,7 +5890,7 @@
         <v>89</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>18</v>
+        <v>303</v>
       </c>
       <c r="AJ35" t="s" s="2">
         <v>101</v>
@@ -5845,7 +5902,7 @@
         <v>18</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>134</v>
+        <v>304</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>18</v>
@@ -5854,47 +5911,45 @@
         <v>18</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>317</v>
+        <v>305</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="C36" t="s" s="2">
-        <v>318</v>
-      </c>
+        <v>306</v>
+      </c>
+      <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>208</v>
+        <v>18</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="G36" t="s" s="2">
         <v>89</v>
       </c>
       <c r="H36" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I36" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J36" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="I36" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="J36" t="s" s="2">
-        <v>18</v>
-      </c>
       <c r="K36" t="s" s="2">
-        <v>210</v>
+        <v>291</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>211</v>
+        <v>307</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>212</v>
+        <v>308</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>213</v>
+        <v>309</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>18</v>
@@ -5919,11 +5974,13 @@
         <v>18</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="Y36" s="2"/>
+        <v>18</v>
+      </c>
+      <c r="Y36" t="s" s="2">
+        <v>18</v>
+      </c>
       <c r="Z36" t="s" s="2">
-        <v>319</v>
+        <v>18</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>18</v>
@@ -5941,42 +5998,42 @@
         <v>18</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>207</v>
+        <v>310</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>18</v>
+        <v>303</v>
       </c>
       <c r="AJ36" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>218</v>
+        <v>18</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>219</v>
+        <v>18</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>220</v>
+        <v>311</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>221</v>
+        <v>18</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>222</v>
+        <v>18</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>320</v>
+        <v>312</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>227</v>
+        <v>313</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5996,19 +6053,23 @@
         <v>18</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>91</v>
+        <v>314</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>228</v>
+        <v>315</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="N37" s="2"/>
-      <c r="O37" s="2"/>
+        <v>316</v>
+      </c>
+      <c r="N37" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="O37" t="s" s="2">
+        <v>318</v>
+      </c>
       <c r="P37" t="s" s="2">
         <v>18</v>
       </c>
@@ -6056,7 +6117,7 @@
         <v>18</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>230</v>
+        <v>319</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>77</v>
@@ -6065,10 +6126,10 @@
         <v>89</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>231</v>
+        <v>18</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>18</v>
+        <v>101</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>18</v>
@@ -6077,7 +6138,7 @@
         <v>18</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>232</v>
+        <v>320</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>18</v>
@@ -6091,18 +6152,18 @@
         <v>321</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>234</v>
+        <v>322</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>159</v>
+        <v>18</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>18</v>
@@ -6111,21 +6172,23 @@
         <v>18</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>136</v>
+        <v>291</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>235</v>
+        <v>323</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>236</v>
+        <v>324</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="O38" s="2"/>
+        <v>325</v>
+      </c>
+      <c r="O38" t="s" s="2">
+        <v>326</v>
+      </c>
       <c r="P38" t="s" s="2">
         <v>18</v>
       </c>
@@ -6161,31 +6224,31 @@
         <v>18</v>
       </c>
       <c r="AB38" t="s" s="2">
-        <v>139</v>
+        <v>18</v>
       </c>
       <c r="AC38" t="s" s="2">
-        <v>237</v>
+        <v>18</v>
       </c>
       <c r="AD38" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AE38" t="s" s="2">
-        <v>140</v>
+        <v>18</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>238</v>
+        <v>327</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>142</v>
+        <v>101</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>18</v>
@@ -6194,7 +6257,7 @@
         <v>18</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>232</v>
+        <v>328</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>18</v>
@@ -6205,10 +6268,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>322</v>
+        <v>329</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>240</v>
+        <v>330</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6216,10 +6279,10 @@
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>18</v>
@@ -6231,13 +6294,13 @@
         <v>90</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>241</v>
+        <v>331</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>242</v>
+        <v>332</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>243</v>
+        <v>333</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -6288,7 +6351,7 @@
         <v>18</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>244</v>
+        <v>334</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>77</v>
@@ -6318,26 +6381,28 @@
         <v>18</v>
       </c>
     </row>
-    <row r="40" hidden="true">
+    <row r="40">
       <c r="A40" t="s" s="2">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="C40" s="2"/>
+        <v>233</v>
+      </c>
+      <c r="C40" t="s" s="2">
+        <v>336</v>
+      </c>
       <c r="D40" t="s" s="2">
-        <v>18</v>
+        <v>234</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="G40" t="s" s="2">
         <v>89</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>18</v>
@@ -6346,16 +6411,18 @@
         <v>18</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>91</v>
+        <v>236</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>228</v>
+        <v>337</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>229</v>
+        <v>238</v>
       </c>
       <c r="N40" s="2"/>
-      <c r="O40" s="2"/>
+      <c r="O40" t="s" s="2">
+        <v>239</v>
+      </c>
       <c r="P40" t="s" s="2">
         <v>18</v>
       </c>
@@ -6379,13 +6446,11 @@
         <v>18</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="Y40" t="s" s="2">
-        <v>18</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="Y40" s="2"/>
       <c r="Z40" t="s" s="2">
-        <v>18</v>
+        <v>338</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>18</v>
@@ -6403,53 +6468,53 @@
         <v>18</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>231</v>
+        <v>18</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>18</v>
+        <v>101</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>18</v>
+        <v>244</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>18</v>
+        <v>245</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>232</v>
+        <v>246</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>18</v>
+        <v>247</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>18</v>
+        <v>248</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>324</v>
+        <v>339</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>159</v>
+        <v>18</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>18</v>
@@ -6461,17 +6526,15 @@
         <v>18</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>136</v>
+        <v>91</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>235</v>
+        <v>184</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>162</v>
-      </c>
+        <v>185</v>
+      </c>
+      <c r="N41" s="2"/>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>18</v>
@@ -6508,31 +6571,31 @@
         <v>18</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>139</v>
+        <v>18</v>
       </c>
       <c r="AC41" t="s" s="2">
-        <v>237</v>
+        <v>18</v>
       </c>
       <c r="AD41" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>140</v>
+        <v>18</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>238</v>
+        <v>186</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>18</v>
+        <v>187</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>142</v>
+        <v>18</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>18</v>
@@ -6541,7 +6604,7 @@
         <v>18</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>232</v>
+        <v>188</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>18</v>
@@ -6552,14 +6615,14 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>325</v>
+        <v>340</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>18</v>
+        <v>159</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -6575,23 +6638,21 @@
         <v>18</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>251</v>
+        <v>136</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>252</v>
+        <v>190</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>253</v>
+        <v>191</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>254</v>
-      </c>
-      <c r="O42" t="s" s="2">
-        <v>255</v>
-      </c>
+        <v>162</v>
+      </c>
+      <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>18</v>
       </c>
@@ -6627,19 +6688,19 @@
         <v>18</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>18</v>
+        <v>139</v>
       </c>
       <c r="AC42" t="s" s="2">
-        <v>18</v>
+        <v>192</v>
       </c>
       <c r="AD42" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>18</v>
+        <v>140</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>256</v>
+        <v>193</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>77</v>
@@ -6651,7 +6712,7 @@
         <v>18</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>101</v>
+        <v>142</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>18</v>
@@ -6660,7 +6721,7 @@
         <v>18</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>257</v>
+        <v>188</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>18</v>
@@ -6671,10 +6732,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>326</v>
+        <v>341</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6682,7 +6743,7 @@
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="G43" t="s" s="2">
         <v>89</v>
@@ -6694,16 +6755,16 @@
         <v>18</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>91</v>
+        <v>259</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>228</v>
+        <v>260</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>229</v>
+        <v>261</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -6754,7 +6815,7 @@
         <v>18</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>230</v>
+        <v>262</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>77</v>
@@ -6763,10 +6824,10 @@
         <v>89</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>231</v>
+        <v>18</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>18</v>
+        <v>101</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>18</v>
@@ -6775,7 +6836,7 @@
         <v>18</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>232</v>
+        <v>134</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>18</v>
@@ -6786,21 +6847,21 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>327</v>
+        <v>342</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>159</v>
+        <v>18</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>18</v>
@@ -6812,17 +6873,15 @@
         <v>18</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>136</v>
+        <v>91</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>235</v>
+        <v>184</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>162</v>
-      </c>
+        <v>185</v>
+      </c>
+      <c r="N44" s="2"/>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>18</v>
@@ -6859,31 +6918,31 @@
         <v>18</v>
       </c>
       <c r="AB44" t="s" s="2">
-        <v>139</v>
+        <v>18</v>
       </c>
       <c r="AC44" t="s" s="2">
-        <v>237</v>
+        <v>18</v>
       </c>
       <c r="AD44" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AE44" t="s" s="2">
-        <v>140</v>
+        <v>18</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>238</v>
+        <v>186</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>18</v>
+        <v>187</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>142</v>
+        <v>18</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>18</v>
@@ -6892,7 +6951,7 @@
         <v>18</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>232</v>
+        <v>188</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>18</v>
@@ -6903,21 +6962,21 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>328</v>
+        <v>343</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>18</v>
+        <v>159</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>18</v>
@@ -6926,23 +6985,21 @@
         <v>18</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>103</v>
+        <v>136</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>264</v>
+        <v>190</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>265</v>
+        <v>191</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="O45" t="s" s="2">
-        <v>267</v>
-      </c>
+        <v>162</v>
+      </c>
+      <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>18</v>
       </c>
@@ -6951,7 +7008,7 @@
         <v>18</v>
       </c>
       <c r="S45" t="s" s="2">
-        <v>329</v>
+        <v>18</v>
       </c>
       <c r="T45" t="s" s="2">
         <v>18</v>
@@ -6978,31 +7035,31 @@
         <v>18</v>
       </c>
       <c r="AB45" t="s" s="2">
-        <v>18</v>
+        <v>139</v>
       </c>
       <c r="AC45" t="s" s="2">
-        <v>18</v>
+        <v>192</v>
       </c>
       <c r="AD45" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AE45" t="s" s="2">
-        <v>18</v>
+        <v>140</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>269</v>
+        <v>193</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>101</v>
+        <v>142</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>18</v>
@@ -7011,7 +7068,7 @@
         <v>18</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>270</v>
+        <v>188</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>18</v>
@@ -7022,10 +7079,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>330</v>
+        <v>344</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7033,10 +7090,10 @@
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>18</v>
@@ -7048,18 +7105,20 @@
         <v>90</v>
       </c>
       <c r="K46" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="L46" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="M46" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="N46" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="O46" t="s" s="2">
         <v>273</v>
       </c>
-      <c r="L46" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>276</v>
-      </c>
-      <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>18</v>
       </c>
@@ -7107,13 +7166,13 @@
         <v>18</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>18</v>
@@ -7128,7 +7187,7 @@
         <v>18</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>18</v>
@@ -7139,10 +7198,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>331</v>
+        <v>345</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7162,21 +7221,19 @@
         <v>18</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>109</v>
+        <v>91</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>281</v>
+        <v>184</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>282</v>
+        <v>185</v>
       </c>
       <c r="N47" s="2"/>
-      <c r="O47" t="s" s="2">
-        <v>283</v>
-      </c>
+      <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>18</v>
       </c>
@@ -7224,7 +7281,7 @@
         <v>18</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>284</v>
+        <v>186</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>77</v>
@@ -7233,10 +7290,10 @@
         <v>89</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>285</v>
+        <v>187</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>101</v>
+        <v>18</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>18</v>
@@ -7245,7 +7302,7 @@
         <v>18</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>286</v>
+        <v>188</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>18</v>
@@ -7256,21 +7313,21 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>332</v>
+        <v>346</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>288</v>
+        <v>279</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>18</v>
+        <v>159</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>18</v>
@@ -7279,21 +7336,21 @@
         <v>18</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>273</v>
+        <v>136</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>289</v>
+        <v>190</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>290</v>
-      </c>
-      <c r="N48" s="2"/>
-      <c r="O48" t="s" s="2">
-        <v>291</v>
-      </c>
+        <v>191</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>18</v>
       </c>
@@ -7329,31 +7386,31 @@
         <v>18</v>
       </c>
       <c r="AB48" t="s" s="2">
-        <v>18</v>
+        <v>139</v>
       </c>
       <c r="AC48" t="s" s="2">
-        <v>18</v>
+        <v>192</v>
       </c>
       <c r="AD48" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AE48" t="s" s="2">
-        <v>18</v>
+        <v>140</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>292</v>
+        <v>193</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>285</v>
+        <v>18</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>101</v>
+        <v>142</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>18</v>
@@ -7362,7 +7419,7 @@
         <v>18</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>293</v>
+        <v>188</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>18</v>
@@ -7373,10 +7430,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>333</v>
+        <v>347</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>295</v>
+        <v>281</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7384,7 +7441,7 @@
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="G49" t="s" s="2">
         <v>89</v>
@@ -7399,19 +7456,19 @@
         <v>90</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>296</v>
+        <v>103</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>297</v>
+        <v>282</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>298</v>
+        <v>283</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>299</v>
+        <v>284</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>300</v>
+        <v>285</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>18</v>
@@ -7421,7 +7478,7 @@
         <v>18</v>
       </c>
       <c r="S49" t="s" s="2">
-        <v>18</v>
+        <v>348</v>
       </c>
       <c r="T49" t="s" s="2">
         <v>18</v>
@@ -7460,7 +7517,7 @@
         <v>18</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>301</v>
+        <v>287</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>77</v>
@@ -7481,7 +7538,7 @@
         <v>18</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>302</v>
+        <v>288</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>18</v>
@@ -7492,10 +7549,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>334</v>
+        <v>349</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>304</v>
+        <v>290</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7518,20 +7575,18 @@
         <v>90</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>273</v>
+        <v>291</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>305</v>
+        <v>292</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>306</v>
+        <v>293</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>307</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>308</v>
-      </c>
+        <v>294</v>
+      </c>
+      <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>18</v>
       </c>
@@ -7579,7 +7634,7 @@
         <v>18</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>309</v>
+        <v>295</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>77</v>
@@ -7600,7 +7655,7 @@
         <v>18</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>310</v>
+        <v>296</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>18</v>
@@ -7611,10 +7666,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>335</v>
+        <v>350</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>312</v>
+        <v>298</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7637,16 +7692,18 @@
         <v>90</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>313</v>
+        <v>109</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>314</v>
+        <v>299</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>315</v>
+        <v>300</v>
       </c>
       <c r="N51" s="2"/>
-      <c r="O51" s="2"/>
+      <c r="O51" t="s" s="2">
+        <v>301</v>
+      </c>
       <c r="P51" t="s" s="2">
         <v>18</v>
       </c>
@@ -7694,7 +7751,7 @@
         <v>18</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>316</v>
+        <v>302</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>77</v>
@@ -7703,7 +7760,7 @@
         <v>89</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>18</v>
+        <v>303</v>
       </c>
       <c r="AJ51" t="s" s="2">
         <v>101</v>
@@ -7715,7 +7772,7 @@
         <v>18</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>134</v>
+        <v>304</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>18</v>
@@ -7726,10 +7783,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>336</v>
+        <v>351</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>336</v>
+        <v>306</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7749,19 +7806,21 @@
         <v>18</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>241</v>
+        <v>291</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>337</v>
+        <v>307</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>338</v>
+        <v>308</v>
       </c>
       <c r="N52" s="2"/>
-      <c r="O52" s="2"/>
+      <c r="O52" t="s" s="2">
+        <v>309</v>
+      </c>
       <c r="P52" t="s" s="2">
         <v>18</v>
       </c>
@@ -7785,13 +7844,13 @@
         <v>18</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>214</v>
+        <v>18</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>339</v>
+        <v>18</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>340</v>
+        <v>18</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>18</v>
@@ -7809,7 +7868,7 @@
         <v>18</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>336</v>
+        <v>310</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>77</v>
@@ -7818,33 +7877,33 @@
         <v>89</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>18</v>
+        <v>303</v>
       </c>
       <c r="AJ52" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>341</v>
+        <v>18</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>219</v>
+        <v>18</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>342</v>
+        <v>311</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>221</v>
+        <v>18</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>343</v>
+        <v>18</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>344</v>
+        <v>352</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>344</v>
+        <v>313</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7855,7 +7914,7 @@
         <v>77</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>18</v>
@@ -7864,19 +7923,23 @@
         <v>18</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>345</v>
+        <v>314</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>346</v>
+        <v>315</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>347</v>
-      </c>
-      <c r="N53" s="2"/>
-      <c r="O53" s="2"/>
+        <v>316</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="O53" t="s" s="2">
+        <v>318</v>
+      </c>
       <c r="P53" t="s" s="2">
         <v>18</v>
       </c>
@@ -7924,13 +7987,13 @@
         <v>18</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>344</v>
+        <v>319</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>18</v>
@@ -7939,16 +8002,16 @@
         <v>101</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>341</v>
+        <v>18</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>219</v>
+        <v>18</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>342</v>
+        <v>320</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>221</v>
+        <v>18</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>18</v>
@@ -7956,10 +8019,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>348</v>
+        <v>322</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7979,20 +8042,22 @@
         <v>18</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>349</v>
+        <v>291</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>350</v>
+        <v>323</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>351</v>
-      </c>
-      <c r="N54" s="2"/>
+        <v>324</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>325</v>
+      </c>
       <c r="O54" t="s" s="2">
-        <v>352</v>
+        <v>326</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>18</v>
@@ -8041,7 +8106,7 @@
         <v>18</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>348</v>
+        <v>327</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>77</v>
@@ -8056,16 +8121,16 @@
         <v>101</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>353</v>
+        <v>18</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>354</v>
+        <v>18</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>355</v>
+        <v>328</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>356</v>
+        <v>18</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>18</v>
@@ -8073,10 +8138,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>357</v>
+        <v>330</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8087,7 +8152,7 @@
         <v>77</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>18</v>
@@ -8096,16 +8161,16 @@
         <v>18</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>358</v>
+        <v>331</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>359</v>
+        <v>332</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>360</v>
+        <v>333</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -8156,7 +8221,7 @@
         <v>18</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>357</v>
+        <v>334</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>77</v>
@@ -8171,27 +8236,27 @@
         <v>101</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>341</v>
+        <v>18</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>219</v>
+        <v>18</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>342</v>
+        <v>134</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>221</v>
+        <v>18</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>18</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>361</v>
+        <v>355</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>361</v>
+        <v>355</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8199,35 +8264,31 @@
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="H56" t="s" s="2">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="I56" t="s" s="2">
         <v>18</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>362</v>
+        <v>259</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>363</v>
+        <v>356</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="O56" t="s" s="2">
-        <v>366</v>
-      </c>
+        <v>357</v>
+      </c>
+      <c r="N56" s="2"/>
+      <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>18</v>
       </c>
@@ -8251,13 +8312,13 @@
         <v>18</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>18</v>
+        <v>240</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>18</v>
+        <v>358</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>18</v>
+        <v>359</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>18</v>
@@ -8275,42 +8336,42 @@
         <v>18</v>
       </c>
       <c r="AF56" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="AG56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH56" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI56" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AJ56" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK56" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="AL56" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="AM56" t="s" s="2">
         <v>361</v>
       </c>
-      <c r="AG56" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AH56" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI56" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AJ56" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="AK56" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="AL56" t="s" s="2">
-        <v>369</v>
-      </c>
-      <c r="AM56" t="s" s="2">
-        <v>370</v>
-      </c>
       <c r="AN56" t="s" s="2">
-        <v>371</v>
+        <v>247</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>372</v>
+        <v>362</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>373</v>
+        <v>363</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>373</v>
+        <v>363</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8321,7 +8382,7 @@
         <v>77</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>18</v>
@@ -8333,13 +8394,13 @@
         <v>18</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>273</v>
+        <v>364</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>228</v>
+        <v>365</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>229</v>
+        <v>366</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -8390,31 +8451,31 @@
         <v>18</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>230</v>
+        <v>363</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>231</v>
+        <v>18</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>18</v>
+        <v>101</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>18</v>
+        <v>360</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>18</v>
+        <v>245</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>232</v>
+        <v>361</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>18</v>
+        <v>247</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>18</v>
@@ -8422,21 +8483,21 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>374</v>
+        <v>367</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>374</v>
+        <v>367</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>159</v>
+        <v>18</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>18</v>
@@ -8448,18 +8509,18 @@
         <v>18</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>136</v>
+        <v>368</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>235</v>
+        <v>369</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="O58" s="2"/>
+        <v>370</v>
+      </c>
+      <c r="N58" s="2"/>
+      <c r="O58" t="s" s="2">
+        <v>371</v>
+      </c>
       <c r="P58" t="s" s="2">
         <v>18</v>
       </c>
@@ -8507,31 +8568,31 @@
         <v>18</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>238</v>
+        <v>367</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>142</v>
+        <v>101</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>18</v>
+        <v>372</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>18</v>
+        <v>373</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>232</v>
+        <v>374</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>18</v>
+        <v>375</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>18</v>
@@ -8539,46 +8600,42 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>376</v>
+        <v>18</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>18</v>
       </c>
       <c r="I59" t="s" s="2">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>136</v>
+        <v>377</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>378</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="O59" t="s" s="2">
-        <v>163</v>
-      </c>
+        <v>379</v>
+      </c>
+      <c r="N59" s="2"/>
+      <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>18</v>
       </c>
@@ -8626,37 +8683,37 @@
         <v>18</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>142</v>
+        <v>101</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>18</v>
+        <v>360</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>18</v>
+        <v>245</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>134</v>
+        <v>361</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>18</v>
+        <v>247</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>18</v>
       </c>
     </row>
-    <row r="60" hidden="true">
+    <row r="60">
       <c r="A60" t="s" s="2">
         <v>380</v>
       </c>
@@ -8669,13 +8726,13 @@
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="H60" t="s" s="2">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="I60" t="s" s="2">
         <v>18</v>
@@ -8684,19 +8741,19 @@
         <v>90</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>241</v>
+        <v>381</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>18</v>
@@ -8721,13 +8778,13 @@
         <v>18</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>214</v>
+        <v>18</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>385</v>
+        <v>18</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>386</v>
+        <v>18</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>18</v>
@@ -8748,39 +8805,39 @@
         <v>380</v>
       </c>
       <c r="AG60" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>101</v>
+        <v>386</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>387</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>18</v>
+        <v>388</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8791,7 +8848,7 @@
         <v>77</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>18</v>
@@ -8803,20 +8860,16 @@
         <v>18</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>241</v>
+        <v>291</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>392</v>
+        <v>184</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>393</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>395</v>
-      </c>
+        <v>185</v>
+      </c>
+      <c r="N61" s="2"/>
+      <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>18</v>
       </c>
@@ -8840,13 +8893,13 @@
         <v>18</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>214</v>
+        <v>18</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>396</v>
+        <v>18</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>397</v>
+        <v>18</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>18</v>
@@ -8864,19 +8917,19 @@
         <v>18</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>391</v>
+        <v>186</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>18</v>
+        <v>187</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>101</v>
+        <v>18</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>18</v>
@@ -8885,32 +8938,32 @@
         <v>18</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>398</v>
+        <v>188</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>399</v>
+        <v>18</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>400</v>
+        <v>393</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>400</v>
+        <v>393</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>18</v>
+        <v>159</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>18</v>
@@ -8919,18 +8972,20 @@
         <v>18</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>401</v>
+        <v>136</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>402</v>
+        <v>190</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="N62" s="2"/>
+        <v>191</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>162</v>
+      </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>18</v>
@@ -8979,28 +9034,28 @@
         <v>18</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>400</v>
+        <v>193</v>
       </c>
       <c r="AG62" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>404</v>
+        <v>18</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>101</v>
+        <v>142</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>405</v>
+        <v>18</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>406</v>
+        <v>18</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>407</v>
+        <v>188</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>18</v>
@@ -9011,42 +9066,46 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>408</v>
+        <v>394</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>408</v>
+        <v>394</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>18</v>
+        <v>395</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>18</v>
       </c>
       <c r="I63" t="s" s="2">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>409</v>
+        <v>136</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>410</v>
+        <v>396</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>411</v>
-      </c>
-      <c r="N63" s="2"/>
-      <c r="O63" s="2"/>
+        <v>397</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="O63" t="s" s="2">
+        <v>163</v>
+      </c>
       <c r="P63" t="s" s="2">
         <v>18</v>
       </c>
@@ -9094,19 +9153,19 @@
         <v>18</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>408</v>
+        <v>398</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>404</v>
+        <v>18</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>101</v>
+        <v>142</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>18</v>
@@ -9115,7 +9174,7 @@
         <v>18</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>412</v>
+        <v>134</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>18</v>
@@ -9124,12 +9183,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>413</v>
+        <v>399</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>413</v>
+        <v>399</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9137,13 +9196,13 @@
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="H64" t="s" s="2">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="I64" t="s" s="2">
         <v>18</v>
@@ -9152,16 +9211,20 @@
         <v>90</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>362</v>
+        <v>259</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>414</v>
+        <v>400</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="N64" s="2"/>
-      <c r="O64" s="2"/>
+        <v>401</v>
+      </c>
+      <c r="N64" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="O64" t="s" s="2">
+        <v>403</v>
+      </c>
       <c r="P64" t="s" s="2">
         <v>18</v>
       </c>
@@ -9185,13 +9248,13 @@
         <v>18</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>18</v>
+        <v>240</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>18</v>
+        <v>404</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>18</v>
+        <v>405</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>18</v>
@@ -9209,13 +9272,13 @@
         <v>18</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>413</v>
+        <v>399</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>18</v>
@@ -9224,27 +9287,27 @@
         <v>101</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>18</v>
+        <v>406</v>
       </c>
       <c r="AL64" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>416</v>
+        <v>407</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>417</v>
+        <v>408</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>418</v>
+        <v>409</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>419</v>
+        <v>410</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>419</v>
+        <v>410</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9255,7 +9318,7 @@
         <v>77</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>18</v>
@@ -9267,16 +9330,20 @@
         <v>18</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>273</v>
+        <v>259</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>228</v>
+        <v>411</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="N65" s="2"/>
-      <c r="O65" s="2"/>
+        <v>412</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="O65" t="s" s="2">
+        <v>414</v>
+      </c>
       <c r="P65" t="s" s="2">
         <v>18</v>
       </c>
@@ -9300,13 +9367,13 @@
         <v>18</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>18</v>
+        <v>240</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>18</v>
+        <v>415</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>18</v>
+        <v>416</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>18</v>
@@ -9324,19 +9391,19 @@
         <v>18</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>230</v>
+        <v>410</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>231</v>
+        <v>18</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>18</v>
+        <v>101</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>18</v>
@@ -9345,32 +9412,32 @@
         <v>18</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>232</v>
+        <v>417</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>18</v>
+        <v>418</v>
       </c>
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>159</v>
+        <v>18</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>18</v>
@@ -9379,20 +9446,18 @@
         <v>18</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>136</v>
+        <v>420</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>235</v>
+        <v>421</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>162</v>
-      </c>
+        <v>422</v>
+      </c>
+      <c r="N66" s="2"/>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>18</v>
@@ -9441,28 +9506,28 @@
         <v>18</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>238</v>
+        <v>419</v>
       </c>
       <c r="AG66" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>18</v>
+        <v>423</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>142</v>
+        <v>101</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>18</v>
+        <v>424</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>18</v>
+        <v>425</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>232</v>
+        <v>426</v>
       </c>
       <c r="AN66" t="s" s="2">
         <v>18</v>
@@ -9473,46 +9538,42 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>421</v>
+        <v>427</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>421</v>
+        <v>427</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>376</v>
+        <v>18</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>18</v>
       </c>
       <c r="I67" t="s" s="2">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>136</v>
+        <v>428</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>377</v>
+        <v>429</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>378</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="O67" t="s" s="2">
-        <v>163</v>
-      </c>
+        <v>430</v>
+      </c>
+      <c r="N67" s="2"/>
+      <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>18</v>
       </c>
@@ -9560,19 +9621,19 @@
         <v>18</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>379</v>
+        <v>427</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>18</v>
+        <v>423</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>142</v>
+        <v>101</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>18</v>
@@ -9581,7 +9642,7 @@
         <v>18</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>134</v>
+        <v>431</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>18</v>
@@ -9590,12 +9651,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="68" hidden="true">
+    <row r="68">
       <c r="A68" t="s" s="2">
-        <v>422</v>
+        <v>432</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>422</v>
+        <v>432</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9606,10 +9667,10 @@
         <v>89</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="H68" t="s" s="2">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="I68" t="s" s="2">
         <v>18</v>
@@ -9618,13 +9679,13 @@
         <v>90</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>109</v>
+        <v>381</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>423</v>
+        <v>433</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>424</v>
+        <v>434</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -9636,7 +9697,7 @@
         <v>18</v>
       </c>
       <c r="S68" t="s" s="2">
-        <v>425</v>
+        <v>18</v>
       </c>
       <c r="T68" t="s" s="2">
         <v>18</v>
@@ -9651,13 +9712,13 @@
         <v>18</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>113</v>
+        <v>18</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>426</v>
+        <v>18</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>427</v>
+        <v>18</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>18</v>
@@ -9675,13 +9736,13 @@
         <v>18</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>422</v>
+        <v>432</v>
       </c>
       <c r="AG68" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>18</v>
@@ -9696,21 +9757,21 @@
         <v>18</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>428</v>
+        <v>435</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>429</v>
+        <v>436</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>430</v>
+        <v>437</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>431</v>
+        <v>438</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>431</v>
+        <v>438</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9718,7 +9779,7 @@
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="G69" t="s" s="2">
         <v>89</v>
@@ -9730,20 +9791,18 @@
         <v>18</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>432</v>
+        <v>291</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>433</v>
+        <v>184</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>435</v>
-      </c>
+        <v>185</v>
+      </c>
+      <c r="N69" s="2"/>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>18</v>
@@ -9792,19 +9851,19 @@
         <v>18</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>431</v>
+        <v>186</v>
       </c>
       <c r="AG69" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="AH69" t="s" s="2">
         <v>89</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>18</v>
+        <v>187</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>101</v>
+        <v>18</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>18</v>
@@ -9813,25 +9872,25 @@
         <v>18</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>436</v>
+        <v>188</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>356</v>
+        <v>18</v>
       </c>
       <c r="AO69" t="s" s="2">
-        <v>173</v>
+        <v>18</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>18</v>
+        <v>159</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
@@ -9850,16 +9909,16 @@
         <v>18</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>79</v>
+        <v>136</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>438</v>
+        <v>190</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>439</v>
+        <v>191</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>440</v>
+        <v>162</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -9909,7 +9968,7 @@
         <v>18</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>437</v>
+        <v>193</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>77</v>
@@ -9921,7 +9980,7 @@
         <v>18</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>101</v>
+        <v>142</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>18</v>
@@ -9930,25 +9989,25 @@
         <v>18</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>441</v>
+        <v>188</v>
       </c>
       <c r="AN70" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AO70" t="s" s="2">
-        <v>442</v>
+        <v>18</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>18</v>
+        <v>395</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
@@ -9961,22 +10020,26 @@
         <v>18</v>
       </c>
       <c r="I71" t="s" s="2">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>444</v>
+        <v>136</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>445</v>
+        <v>396</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="N71" s="2"/>
-      <c r="O71" s="2"/>
+        <v>397</v>
+      </c>
+      <c r="N71" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="O71" t="s" s="2">
+        <v>163</v>
+      </c>
       <c r="P71" t="s" s="2">
         <v>18</v>
       </c>
@@ -10024,7 +10087,7 @@
         <v>18</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>443</v>
+        <v>398</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>77</v>
@@ -10036,26 +10099,490 @@
         <v>18</v>
       </c>
       <c r="AJ71" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="AK71" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AL71" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AM71" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="AN71" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AO71" t="s" s="2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="72" hidden="true">
+      <c r="A72" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="B72" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="C72" s="2"/>
+      <c r="D72" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="E72" s="2"/>
+      <c r="F72" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="G72" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H72" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I72" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J72" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K72" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="L72" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="M72" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="N72" s="2"/>
+      <c r="O72" s="2"/>
+      <c r="P72" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Q72" s="2"/>
+      <c r="R72" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="S72" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="T72" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="U72" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="V72" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="W72" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="X72" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="Y72" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="Z72" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="AA72" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AB72" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AC72" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AD72" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AE72" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AF72" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="AG72" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AH72" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI72" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AJ72" t="s" s="2">
         <v>101</v>
       </c>
-      <c r="AK71" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AL71" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AM71" t="s" s="2">
+      <c r="AK72" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AL72" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AM72" t="s" s="2">
         <v>447</v>
       </c>
-      <c r="AN71" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AO71" t="s" s="2">
+      <c r="AN72" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="AO72" t="s" s="2">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="73" hidden="true">
+      <c r="A73" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="B73" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="C73" s="2"/>
+      <c r="D73" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="E73" s="2"/>
+      <c r="F73" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="G73" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H73" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I73" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J73" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K73" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="L73" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="M73" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="N73" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="O73" s="2"/>
+      <c r="P73" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Q73" s="2"/>
+      <c r="R73" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="S73" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="T73" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="U73" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="V73" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="W73" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="X73" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Y73" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Z73" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AA73" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AB73" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AC73" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AD73" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AE73" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AF73" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="AG73" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AH73" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI73" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AJ73" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK73" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AL73" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AM73" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="AN73" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="AO73" t="s" s="2">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="74" hidden="true">
+      <c r="A74" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="B74" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="C74" s="2"/>
+      <c r="D74" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="E74" s="2"/>
+      <c r="F74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H74" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I74" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J74" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="K74" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="L74" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="M74" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="N74" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="O74" s="2"/>
+      <c r="P74" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Q74" s="2"/>
+      <c r="R74" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="S74" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="T74" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="U74" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="V74" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="W74" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="X74" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Y74" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Z74" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AA74" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AB74" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AC74" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AD74" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AE74" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AF74" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="AG74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI74" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AJ74" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK74" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AL74" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AM74" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="AN74" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AO74" t="s" s="2">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="75" hidden="true">
+      <c r="A75" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="B75" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="C75" s="2"/>
+      <c r="D75" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="E75" s="2"/>
+      <c r="F75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G75" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H75" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I75" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J75" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="K75" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="L75" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="M75" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="N75" s="2"/>
+      <c r="O75" s="2"/>
+      <c r="P75" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Q75" s="2"/>
+      <c r="R75" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="S75" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="T75" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="U75" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="V75" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="W75" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="X75" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Y75" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Z75" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AA75" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AB75" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AC75" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AD75" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AE75" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AF75" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="AG75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH75" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI75" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AJ75" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK75" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AL75" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AM75" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="AN75" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AO75" t="s" s="2">
         <v>18</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO71">
+  <autoFilter ref="A1:AO75">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -10065,7 +10592,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI70">
+  <conditionalFormatting sqref="A2:AI74">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/r5-aist-trustworthyai-main/StructureDefinition-eu-ai-provenance.xlsx
+++ b/r5-aist-trustworthyai-main/StructureDefinition-eu-ai-provenance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T11:07:29+00:00</t>
+    <t>2026-09-02T10:48:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-aist-trustworthyai-main/StructureDefinition-eu-ai-provenance.xlsx
+++ b/r5-aist-trustworthyai-main/StructureDefinition-eu-ai-provenance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T10:48:14+00:00</t>
+    <t>2026-09-03T11:53:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-aist-trustworthyai-main/StructureDefinition-eu-ai-provenance.xlsx
+++ b/r5-aist-trustworthyai-main/StructureDefinition-eu-ai-provenance.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$75</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$77</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2803" uniqueCount="467">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2877" uniqueCount="477">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T11:53:05+00:00</t>
+    <t>2026-09-07T08:39:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -440,6 +440,9 @@
     <t>Provenance.extension</t>
   </si>
   <si>
+    <t>3</t>
+  </si>
+  <si>
     <t xml:space="preserve">Extension
 </t>
   </si>
@@ -512,6 +515,38 @@
     <t>Records the identifier of an EHDS data permit associated with the documented secondary use, where applicable.</t>
   </si>
   <si>
+    <t>Provenance.extension:caseIndication</t>
+  </si>
+  <si>
+    <t>caseIndication</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://example.org/fhir/eu-ai-transparency/StructureDefinition/case-specific-indication}
+</t>
+  </si>
+  <si>
+    <t>Clinical reason for AI use</t>
+  </si>
+  <si>
+    <t>Records the clinical indication or case-specific reason for applying the AI system in the documented patient context.</t>
+  </si>
+  <si>
+    <t>Provenance.extension:automatedDecision</t>
+  </si>
+  <si>
+    <t>automatedDecision</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://example.org/fhir/eu-ai-transparency/StructureDefinition/automated-decision-flag}
+</t>
+  </si>
+  <si>
+    <t>Automated decision flag</t>
+  </si>
+  <si>
+    <t>Indicates whether the documented AI-supported processing resulted in a decision made solely by automated means.</t>
+  </si>
+  <si>
     <t>Provenance.modifierExtension</t>
   </si>
   <si>
@@ -538,7 +573,7 @@
     <t>Provenance.target</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://example.org/fhir/eu-ai-transparency/StructureDefinition/eu-ai-observation)
+    <t xml:space="preserve">Reference(Resource|5.0.0)
 </t>
   </si>
   <si>
@@ -570,7 +605,7 @@
 </t>
   </si>
   <si>
-    <t>Execution period of the AI processing activity</t>
+    <t>Period of the activity that generated or influenced the target resource</t>
   </si>
   <si>
     <t>The period during which the activity occurred.</t>
@@ -1365,7 +1400,7 @@
     <t>Provenance.entity</t>
   </si>
   <si>
-    <t>An entity used in this activity</t>
+    <t>Input data used to generate the AI output</t>
   </si>
   <si>
     <t>An entity used in this activity.</t>
@@ -1419,11 +1454,7 @@
     <t>Provenance.entity.what</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Observation|ImagingStudy|DocumentReference)
-</t>
-  </si>
-  <si>
-    <t>Source data processed by the AI</t>
+    <t>Source data processed by the AI system</t>
   </si>
   <si>
     <t>Identity of the  Entity used. May be a logical or physical uri and maybe absolute or relative.</t>
@@ -1775,7 +1806,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO75"/>
+  <dimension ref="A1:AO77"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="59.31640625" customWidth="true" bestFit="true"/>
@@ -2775,7 +2806,7 @@
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
-        <v>89</v>
+        <v>136</v>
       </c>
       <c r="G9" t="s" s="2">
         <v>78</v>
@@ -2790,13 +2821,13 @@
         <v>18</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -2835,17 +2866,17 @@
         <v>18</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AC9" s="2"/>
       <c r="AD9" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>77</v>
@@ -2857,7 +2888,7 @@
         <v>18</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>18</v>
@@ -2877,13 +2908,13 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B10" t="s" s="2">
         <v>135</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D10" t="s" s="2">
         <v>18</v>
@@ -2905,13 +2936,13 @@
         <v>18</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -2962,7 +2993,7 @@
         <v>18</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>77</v>
@@ -2974,7 +3005,7 @@
         <v>18</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>18</v>
@@ -2994,13 +3025,13 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B11" t="s" s="2">
         <v>135</v>
       </c>
       <c r="C11" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D11" t="s" s="2">
         <v>18</v>
@@ -3022,13 +3053,13 @@
         <v>18</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -3079,7 +3110,7 @@
         <v>18</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>77</v>
@@ -3091,7 +3122,7 @@
         <v>18</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AK11" t="s" s="2">
         <v>18</v>
@@ -3111,13 +3142,13 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B12" t="s" s="2">
         <v>135</v>
       </c>
       <c r="C12" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D12" t="s" s="2">
         <v>18</v>
@@ -3139,13 +3170,13 @@
         <v>18</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -3196,7 +3227,7 @@
         <v>18</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>77</v>
@@ -3208,7 +3239,7 @@
         <v>18</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AK12" t="s" s="2">
         <v>18</v>
@@ -3226,48 +3257,46 @@
         <v>18</v>
       </c>
     </row>
-    <row r="13" hidden="true">
+    <row r="13">
       <c r="A13" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="C13" s="2"/>
+        <v>135</v>
+      </c>
+      <c r="C13" t="s" s="2">
+        <v>160</v>
+      </c>
       <c r="D13" t="s" s="2">
-        <v>159</v>
+        <v>18</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="H13" t="s" s="2">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>136</v>
+        <v>161</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="O13" t="s" s="2">
         <v>163</v>
       </c>
+      <c r="N13" s="2"/>
+      <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
         <v>18</v>
       </c>
@@ -3315,7 +3344,7 @@
         <v>18</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>164</v>
+        <v>142</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>77</v>
@@ -3327,7 +3356,7 @@
         <v>18</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AK13" t="s" s="2">
         <v>18</v>
@@ -3336,7 +3365,7 @@
         <v>18</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>134</v>
+        <v>18</v>
       </c>
       <c r="AN13" t="s" s="2">
         <v>18</v>
@@ -3347,12 +3376,14 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="B14" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="C14" t="s" s="2">
         <v>165</v>
       </c>
-      <c r="B14" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
         <v>18</v>
       </c>
@@ -3361,7 +3392,7 @@
         <v>89</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>90</v>
@@ -3370,7 +3401,7 @@
         <v>18</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="K14" t="s" s="2">
         <v>166</v>
@@ -3381,9 +3412,7 @@
       <c r="M14" t="s" s="2">
         <v>168</v>
       </c>
-      <c r="N14" t="s" s="2">
-        <v>169</v>
-      </c>
+      <c r="N14" s="2"/>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>18</v>
@@ -3432,10 +3461,10 @@
         <v>18</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>165</v>
+        <v>142</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="AH14" t="s" s="2">
         <v>78</v>
@@ -3444,64 +3473,66 @@
         <v>18</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>101</v>
+        <v>143</v>
       </c>
       <c r="AK14" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>170</v>
+        <v>18</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>171</v>
+        <v>18</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>172</v>
+        <v>18</v>
       </c>
       <c r="AO14" t="s" s="2">
-        <v>173</v>
+        <v>18</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>18</v>
+        <v>170</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="H15" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I15" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="I15" t="s" s="2">
-        <v>18</v>
-      </c>
       <c r="J15" t="s" s="2">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>175</v>
+        <v>137</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="O15" s="2"/>
+        <v>173</v>
+      </c>
+      <c r="O15" t="s" s="2">
+        <v>174</v>
+      </c>
       <c r="P15" t="s" s="2">
         <v>18</v>
       </c>
@@ -3549,42 +3580,42 @@
         <v>18</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>101</v>
+        <v>143</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>179</v>
+        <v>18</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>180</v>
+        <v>18</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>181</v>
+        <v>134</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>182</v>
+        <v>18</v>
       </c>
       <c r="AO15" t="s" s="2">
         <v>18</v>
       </c>
     </row>
-    <row r="16" hidden="true">
+    <row r="16">
       <c r="A16" t="s" s="2">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3592,30 +3623,32 @@
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="I16" t="s" s="2">
         <v>18</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>91</v>
+        <v>177</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>185</v>
-      </c>
-      <c r="N16" s="2"/>
+        <v>179</v>
+      </c>
+      <c r="N16" t="s" s="2">
+        <v>180</v>
+      </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
         <v>18</v>
@@ -3664,56 +3697,56 @@
         <v>18</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AI16" t="s" s="2">
-        <v>187</v>
+        <v>18</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>18</v>
+        <v>101</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>18</v>
+        <v>181</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>18</v>
+        <v>183</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>18</v>
+        <v>184</v>
       </c>
     </row>
-    <row r="17" hidden="true">
+    <row r="17">
       <c r="A17" t="s" s="2">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>159</v>
+        <v>18</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="I17" t="s" s="2">
         <v>18</v>
@@ -3722,16 +3755,16 @@
         <v>18</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>136</v>
+        <v>186</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>162</v>
+        <v>189</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3769,49 +3802,49 @@
         <v>18</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>139</v>
+        <v>18</v>
       </c>
       <c r="AC17" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AD17" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AE17" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AF17" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="AG17" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH17" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI17" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AJ17" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK17" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="AL17" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="AM17" t="s" s="2">
         <v>192</v>
       </c>
-      <c r="AD17" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AE17" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="AF17" t="s" s="2">
+      <c r="AN17" t="s" s="2">
         <v>193</v>
       </c>
-      <c r="AG17" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH17" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI17" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AJ17" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="AK17" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AL17" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AM17" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="AN17" t="s" s="2">
-        <v>18</v>
-      </c>
       <c r="AO17" t="s" s="2">
         <v>18</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
         <v>194</v>
       </c>
@@ -3824,32 +3857,30 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="G18" t="s" s="2">
         <v>89</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="I18" t="s" s="2">
         <v>18</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="K18" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="L18" t="s" s="2">
         <v>195</v>
       </c>
-      <c r="L18" t="s" s="2">
+      <c r="M18" t="s" s="2">
         <v>196</v>
       </c>
-      <c r="M18" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>198</v>
-      </c>
+      <c r="N18" s="2"/>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>18</v>
@@ -3898,82 +3929,80 @@
         <v>18</v>
       </c>
       <c r="AF18" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="AG18" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH18" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI18" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="AJ18" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AK18" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AL18" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AM18" t="s" s="2">
         <v>199</v>
       </c>
-      <c r="AG18" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH18" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI18" t="s" s="2">
+      <c r="AN18" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AO18" t="s" s="2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="19" hidden="true">
+      <c r="A19" t="s" s="2">
         <v>200</v>
       </c>
-      <c r="AJ18" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK18" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AL18" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AM18" t="s" s="2">
-        <v>201</v>
-      </c>
-      <c r="AN18" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AO18" t="s" s="2">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="s" s="2">
-        <v>202</v>
-      </c>
       <c r="B19" t="s" s="2">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>18</v>
+        <v>170</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="I19" t="s" s="2">
         <v>18</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>195</v>
+        <v>137</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>205</v>
+        <v>173</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>18</v>
       </c>
-      <c r="Q19" t="s" s="2">
-        <v>206</v>
-      </c>
+      <c r="Q19" s="2"/>
       <c r="R19" t="s" s="2">
         <v>18</v>
       </c>
@@ -4005,31 +4034,31 @@
         <v>18</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>18</v>
+        <v>140</v>
       </c>
       <c r="AC19" t="s" s="2">
-        <v>18</v>
+        <v>203</v>
       </c>
       <c r="AD19" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>18</v>
+        <v>141</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>200</v>
+        <v>18</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>101</v>
+        <v>143</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>18</v>
@@ -4038,7 +4067,7 @@
         <v>18</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>208</v>
+        <v>199</v>
       </c>
       <c r="AN19" t="s" s="2">
         <v>18</v>
@@ -4049,10 +4078,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4075,16 +4104,16 @@
         <v>90</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -4134,7 +4163,7 @@
         <v>18</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>77</v>
@@ -4143,7 +4172,7 @@
         <v>89</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>18</v>
+        <v>211</v>
       </c>
       <c r="AJ20" t="s" s="2">
         <v>101</v>
@@ -4152,24 +4181,24 @@
         <v>18</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>214</v>
+        <v>18</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>216</v>
+        <v>18</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>217</v>
+        <v>18</v>
       </c>
     </row>
-    <row r="21" hidden="true">
+    <row r="21">
       <c r="A21" t="s" s="2">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4177,37 +4206,39 @@
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="I21" t="s" s="2">
         <v>18</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>103</v>
+        <v>206</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>18</v>
       </c>
-      <c r="Q21" s="2"/>
+      <c r="Q21" t="s" s="2">
+        <v>217</v>
+      </c>
       <c r="R21" t="s" s="2">
         <v>18</v>
       </c>
@@ -4257,10 +4288,10 @@
         <v>77</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>18</v>
+        <v>211</v>
       </c>
       <c r="AJ21" t="s" s="2">
         <v>101</v>
@@ -4272,21 +4303,21 @@
         <v>18</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>223</v>
+        <v>18</v>
       </c>
     </row>
-    <row r="22" hidden="true">
+    <row r="22">
       <c r="A22" t="s" s="2">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4294,30 +4325,32 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="G22" t="s" s="2">
         <v>89</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="I22" t="s" s="2">
         <v>18</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="N22" s="2"/>
+        <v>223</v>
+      </c>
+      <c r="N22" t="s" s="2">
+        <v>224</v>
+      </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>18</v>
@@ -4366,7 +4399,7 @@
         <v>18</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>77</v>
@@ -4381,41 +4414,41 @@
         <v>101</v>
       </c>
       <c r="AK22" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AL22" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="AM22" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="AN22" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="AO22" t="s" s="2">
         <v>228</v>
-      </c>
-      <c r="AL22" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="AM22" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="AN22" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="AO22" t="s" s="2">
-        <v>232</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>234</v>
+        <v>18</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>235</v>
+        <v>77</v>
       </c>
       <c r="G23" t="s" s="2">
         <v>78</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>18</v>
@@ -4424,18 +4457,18 @@
         <v>18</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>236</v>
+        <v>103</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>238</v>
-      </c>
-      <c r="N23" s="2"/>
-      <c r="O23" t="s" s="2">
-        <v>239</v>
-      </c>
+        <v>231</v>
+      </c>
+      <c r="N23" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>18</v>
       </c>
@@ -4459,29 +4492,31 @@
         <v>18</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>240</v>
+        <v>18</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>241</v>
+        <v>18</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>242</v>
+        <v>18</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>243</v>
-      </c>
-      <c r="AC23" s="2"/>
+        <v>18</v>
+      </c>
+      <c r="AC23" t="s" s="2">
+        <v>18</v>
+      </c>
       <c r="AD23" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>140</v>
+        <v>18</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>77</v>
@@ -4496,43 +4531,41 @@
         <v>101</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>244</v>
+        <v>18</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>245</v>
+        <v>18</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>246</v>
+        <v>233</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>247</v>
+        <v>18</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>248</v>
+        <v>234</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>249</v>
+        <v>235</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="C24" t="s" s="2">
-        <v>250</v>
-      </c>
+        <v>235</v>
+      </c>
+      <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>234</v>
+        <v>18</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="G24" t="s" s="2">
         <v>89</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>18</v>
@@ -4544,15 +4577,13 @@
         <v>236</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>251</v>
+        <v>237</v>
       </c>
       <c r="M24" t="s" s="2">
         <v>238</v>
       </c>
       <c r="N24" s="2"/>
-      <c r="O24" t="s" s="2">
-        <v>239</v>
-      </c>
+      <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>18</v>
       </c>
@@ -4576,11 +4607,13 @@
         <v>18</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="Y24" s="2"/>
+        <v>18</v>
+      </c>
+      <c r="Y24" t="s" s="2">
+        <v>18</v>
+      </c>
       <c r="Z24" t="s" s="2">
-        <v>252</v>
+        <v>18</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>18</v>
@@ -4598,13 +4631,13 @@
         <v>18</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>18</v>
@@ -4613,41 +4646,41 @@
         <v>101</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>248</v>
+        <v>243</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>253</v>
+        <v>244</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>254</v>
+        <v>244</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>18</v>
+        <v>245</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>77</v>
+        <v>246</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="I25" t="s" s="2">
         <v>18</v>
@@ -4656,16 +4689,18 @@
         <v>18</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>91</v>
+        <v>247</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>184</v>
+        <v>248</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>185</v>
+        <v>249</v>
       </c>
       <c r="N25" s="2"/>
-      <c r="O25" s="2"/>
+      <c r="O25" t="s" s="2">
+        <v>250</v>
+      </c>
       <c r="P25" t="s" s="2">
         <v>18</v>
       </c>
@@ -4689,80 +4724,80 @@
         <v>18</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>18</v>
+        <v>251</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>18</v>
+        <v>252</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>18</v>
+        <v>253</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AC25" t="s" s="2">
-        <v>18</v>
-      </c>
+        <v>254</v>
+      </c>
+      <c r="AC25" s="2"/>
       <c r="AD25" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>18</v>
+        <v>141</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>186</v>
+        <v>244</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>187</v>
+        <v>18</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>18</v>
+        <v>101</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>18</v>
+        <v>255</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>18</v>
+        <v>256</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>188</v>
+        <v>257</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>18</v>
+        <v>258</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>18</v>
+        <v>259</v>
       </c>
     </row>
-    <row r="26" hidden="true">
+    <row r="26">
       <c r="A26" t="s" s="2">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="C26" s="2"/>
+        <v>244</v>
+      </c>
+      <c r="C26" t="s" s="2">
+        <v>261</v>
+      </c>
       <c r="D26" t="s" s="2">
-        <v>159</v>
+        <v>245</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="I26" t="s" s="2">
         <v>18</v>
@@ -4771,18 +4806,18 @@
         <v>18</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>136</v>
+        <v>247</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>190</v>
+        <v>262</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="O26" s="2"/>
+        <v>249</v>
+      </c>
+      <c r="N26" s="2"/>
+      <c r="O26" t="s" s="2">
+        <v>250</v>
+      </c>
       <c r="P26" t="s" s="2">
         <v>18</v>
       </c>
@@ -4806,31 +4841,29 @@
         <v>18</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="Y26" t="s" s="2">
-        <v>18</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="Y26" s="2"/>
       <c r="Z26" t="s" s="2">
-        <v>18</v>
+        <v>263</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>139</v>
+        <v>18</v>
       </c>
       <c r="AC26" t="s" s="2">
-        <v>192</v>
+        <v>18</v>
       </c>
       <c r="AD26" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>140</v>
+        <v>18</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>193</v>
+        <v>244</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>77</v>
@@ -4842,30 +4875,30 @@
         <v>18</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>142</v>
+        <v>101</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>18</v>
+        <v>255</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>18</v>
+        <v>256</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>188</v>
+        <v>257</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>18</v>
+        <v>258</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>18</v>
+        <v>259</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>257</v>
+        <v>264</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>258</v>
+        <v>265</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4873,7 +4906,7 @@
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="G27" t="s" s="2">
         <v>89</v>
@@ -4885,16 +4918,16 @@
         <v>18</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>259</v>
+        <v>91</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>260</v>
+        <v>195</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>261</v>
+        <v>196</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -4945,7 +4978,7 @@
         <v>18</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>262</v>
+        <v>197</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>77</v>
@@ -4954,10 +4987,10 @@
         <v>89</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>18</v>
+        <v>198</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>101</v>
+        <v>18</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>18</v>
@@ -4966,7 +4999,7 @@
         <v>18</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>134</v>
+        <v>199</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>18</v>
@@ -4977,21 +5010,21 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>18</v>
+        <v>170</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>18</v>
@@ -5003,15 +5036,17 @@
         <v>18</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>91</v>
+        <v>137</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>184</v>
+        <v>201</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>185</v>
-      </c>
-      <c r="N28" s="2"/>
+        <v>202</v>
+      </c>
+      <c r="N28" t="s" s="2">
+        <v>173</v>
+      </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>18</v>
@@ -5048,31 +5083,31 @@
         <v>18</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>18</v>
+        <v>140</v>
       </c>
       <c r="AC28" t="s" s="2">
-        <v>18</v>
+        <v>203</v>
       </c>
       <c r="AD28" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>18</v>
+        <v>141</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>186</v>
+        <v>204</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>187</v>
+        <v>18</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>18</v>
+        <v>143</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>18</v>
@@ -5081,7 +5116,7 @@
         <v>18</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>188</v>
+        <v>199</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>18</v>
@@ -5092,21 +5127,21 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>159</v>
+        <v>18</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>18</v>
@@ -5115,20 +5150,18 @@
         <v>18</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>136</v>
+        <v>270</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>190</v>
+        <v>271</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>162</v>
-      </c>
+        <v>272</v>
+      </c>
+      <c r="N29" s="2"/>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>18</v>
@@ -5165,31 +5198,31 @@
         <v>18</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>139</v>
+        <v>18</v>
       </c>
       <c r="AC29" t="s" s="2">
-        <v>192</v>
+        <v>18</v>
       </c>
       <c r="AD29" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>140</v>
+        <v>18</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>193</v>
+        <v>273</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>142</v>
+        <v>101</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>18</v>
@@ -5198,7 +5231,7 @@
         <v>18</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>188</v>
+        <v>134</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>18</v>
@@ -5209,10 +5242,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>268</v>
+        <v>275</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5220,10 +5253,10 @@
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>18</v>
@@ -5232,23 +5265,19 @@
         <v>18</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>269</v>
+        <v>91</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>270</v>
+        <v>195</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>273</v>
-      </c>
+        <v>196</v>
+      </c>
+      <c r="N30" s="2"/>
+      <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>18</v>
       </c>
@@ -5296,19 +5325,19 @@
         <v>18</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>274</v>
+        <v>197</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>18</v>
+        <v>198</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>101</v>
+        <v>18</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>18</v>
@@ -5317,7 +5346,7 @@
         <v>18</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>275</v>
+        <v>199</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>18</v>
@@ -5335,14 +5364,14 @@
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>18</v>
+        <v>170</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>18</v>
@@ -5354,15 +5383,17 @@
         <v>18</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>91</v>
+        <v>137</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>184</v>
+        <v>201</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>185</v>
-      </c>
-      <c r="N31" s="2"/>
+        <v>202</v>
+      </c>
+      <c r="N31" t="s" s="2">
+        <v>173</v>
+      </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>18</v>
@@ -5399,31 +5430,31 @@
         <v>18</v>
       </c>
       <c r="AB31" t="s" s="2">
-        <v>18</v>
+        <v>140</v>
       </c>
       <c r="AC31" t="s" s="2">
-        <v>18</v>
+        <v>203</v>
       </c>
       <c r="AD31" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>18</v>
+        <v>141</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>186</v>
+        <v>204</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>187</v>
+        <v>18</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>18</v>
+        <v>143</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>18</v>
@@ -5432,7 +5463,7 @@
         <v>18</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>188</v>
+        <v>199</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>18</v>
@@ -5450,11 +5481,11 @@
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>159</v>
+        <v>18</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="G32" t="s" s="2">
         <v>78</v>
@@ -5466,21 +5497,23 @@
         <v>18</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>136</v>
+        <v>280</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>190</v>
+        <v>281</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>191</v>
+        <v>282</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="O32" s="2"/>
+        <v>283</v>
+      </c>
+      <c r="O32" t="s" s="2">
+        <v>284</v>
+      </c>
       <c r="P32" t="s" s="2">
         <v>18</v>
       </c>
@@ -5516,19 +5549,19 @@
         <v>18</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>139</v>
+        <v>18</v>
       </c>
       <c r="AC32" t="s" s="2">
-        <v>192</v>
+        <v>18</v>
       </c>
       <c r="AD32" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>140</v>
+        <v>18</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>193</v>
+        <v>285</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>77</v>
@@ -5540,7 +5573,7 @@
         <v>18</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>142</v>
+        <v>101</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>18</v>
@@ -5549,7 +5582,7 @@
         <v>18</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>188</v>
+        <v>286</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>18</v>
@@ -5560,10 +5593,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>280</v>
+        <v>287</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>281</v>
+        <v>288</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5571,7 +5604,7 @@
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="G33" t="s" s="2">
         <v>89</v>
@@ -5583,23 +5616,19 @@
         <v>18</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>282</v>
+        <v>195</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="O33" t="s" s="2">
-        <v>285</v>
-      </c>
+        <v>196</v>
+      </c>
+      <c r="N33" s="2"/>
+      <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>18</v>
       </c>
@@ -5608,7 +5637,7 @@
         <v>18</v>
       </c>
       <c r="S33" t="s" s="2">
-        <v>286</v>
+        <v>18</v>
       </c>
       <c r="T33" t="s" s="2">
         <v>18</v>
@@ -5647,7 +5676,7 @@
         <v>18</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>287</v>
+        <v>197</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>77</v>
@@ -5656,10 +5685,10 @@
         <v>89</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>18</v>
+        <v>198</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>101</v>
+        <v>18</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>18</v>
@@ -5668,7 +5697,7 @@
         <v>18</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>288</v>
+        <v>199</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>18</v>
@@ -5686,14 +5715,14 @@
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>18</v>
+        <v>170</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>18</v>
@@ -5702,19 +5731,19 @@
         <v>18</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>291</v>
+        <v>137</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>292</v>
+        <v>201</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>293</v>
+        <v>202</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>294</v>
+        <v>173</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -5752,31 +5781,31 @@
         <v>18</v>
       </c>
       <c r="AB34" t="s" s="2">
-        <v>18</v>
+        <v>140</v>
       </c>
       <c r="AC34" t="s" s="2">
-        <v>18</v>
+        <v>203</v>
       </c>
       <c r="AD34" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AE34" t="s" s="2">
-        <v>18</v>
+        <v>141</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>295</v>
+        <v>204</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>101</v>
+        <v>143</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>18</v>
@@ -5785,7 +5814,7 @@
         <v>18</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>296</v>
+        <v>199</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>18</v>
@@ -5796,10 +5825,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5807,7 +5836,7 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="G35" t="s" s="2">
         <v>89</v>
@@ -5822,17 +5851,19 @@
         <v>90</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="N35" s="2"/>
+        <v>294</v>
+      </c>
+      <c r="N35" t="s" s="2">
+        <v>295</v>
+      </c>
       <c r="O35" t="s" s="2">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>18</v>
@@ -5842,7 +5873,7 @@
         <v>18</v>
       </c>
       <c r="S35" t="s" s="2">
-        <v>18</v>
+        <v>297</v>
       </c>
       <c r="T35" t="s" s="2">
         <v>18</v>
@@ -5881,7 +5912,7 @@
         <v>18</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>77</v>
@@ -5890,7 +5921,7 @@
         <v>89</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>303</v>
+        <v>18</v>
       </c>
       <c r="AJ35" t="s" s="2">
         <v>101</v>
@@ -5902,7 +5933,7 @@
         <v>18</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>18</v>
@@ -5913,10 +5944,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5939,18 +5970,18 @@
         <v>90</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>291</v>
+        <v>302</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="N36" s="2"/>
-      <c r="O36" t="s" s="2">
-        <v>309</v>
-      </c>
+        <v>304</v>
+      </c>
+      <c r="N36" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>18</v>
       </c>
@@ -5998,7 +6029,7 @@
         <v>18</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>77</v>
@@ -6007,7 +6038,7 @@
         <v>89</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>303</v>
+        <v>18</v>
       </c>
       <c r="AJ36" t="s" s="2">
         <v>101</v>
@@ -6019,7 +6050,7 @@
         <v>18</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>18</v>
@@ -6030,10 +6061,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6056,19 +6087,17 @@
         <v>90</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>314</v>
+        <v>109</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>316</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>317</v>
-      </c>
+        <v>311</v>
+      </c>
+      <c r="N37" s="2"/>
       <c r="O37" t="s" s="2">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>18</v>
@@ -6117,7 +6146,7 @@
         <v>18</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>77</v>
@@ -6126,7 +6155,7 @@
         <v>89</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>18</v>
+        <v>314</v>
       </c>
       <c r="AJ37" t="s" s="2">
         <v>101</v>
@@ -6138,7 +6167,7 @@
         <v>18</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>18</v>
@@ -6149,10 +6178,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6175,19 +6204,17 @@
         <v>90</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>291</v>
+        <v>302</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>325</v>
-      </c>
+        <v>319</v>
+      </c>
+      <c r="N38" s="2"/>
       <c r="O38" t="s" s="2">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>18</v>
@@ -6236,7 +6263,7 @@
         <v>18</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>77</v>
@@ -6245,7 +6272,7 @@
         <v>89</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>18</v>
+        <v>314</v>
       </c>
       <c r="AJ38" t="s" s="2">
         <v>101</v>
@@ -6257,7 +6284,7 @@
         <v>18</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>18</v>
@@ -6268,10 +6295,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6282,7 +6309,7 @@
         <v>77</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>18</v>
@@ -6294,16 +6321,20 @@
         <v>90</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>333</v>
-      </c>
-      <c r="N39" s="2"/>
-      <c r="O39" s="2"/>
+        <v>327</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="O39" t="s" s="2">
+        <v>329</v>
+      </c>
       <c r="P39" t="s" s="2">
         <v>18</v>
       </c>
@@ -6351,7 +6382,7 @@
         <v>18</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>77</v>
@@ -6372,7 +6403,7 @@
         <v>18</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>134</v>
+        <v>331</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>18</v>
@@ -6381,47 +6412,47 @@
         <v>18</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="C40" t="s" s="2">
-        <v>336</v>
-      </c>
+        <v>333</v>
+      </c>
+      <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>234</v>
+        <v>18</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="G40" t="s" s="2">
         <v>89</v>
       </c>
       <c r="H40" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I40" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J40" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="I40" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="J40" t="s" s="2">
-        <v>18</v>
-      </c>
       <c r="K40" t="s" s="2">
-        <v>236</v>
+        <v>302</v>
       </c>
       <c r="L40" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="M40" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="N40" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="O40" t="s" s="2">
         <v>337</v>
-      </c>
-      <c r="M40" t="s" s="2">
-        <v>238</v>
-      </c>
-      <c r="N40" s="2"/>
-      <c r="O40" t="s" s="2">
-        <v>239</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>18</v>
@@ -6446,35 +6477,37 @@
         <v>18</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="Y40" s="2"/>
+        <v>18</v>
+      </c>
+      <c r="Y40" t="s" s="2">
+        <v>18</v>
+      </c>
       <c r="Z40" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AA40" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AB40" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AC40" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AD40" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AE40" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AF40" t="s" s="2">
         <v>338</v>
       </c>
-      <c r="AA40" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AB40" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AC40" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AD40" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AE40" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AF40" t="s" s="2">
-        <v>233</v>
-      </c>
       <c r="AG40" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>18</v>
@@ -6483,27 +6516,27 @@
         <v>101</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>244</v>
+        <v>18</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>245</v>
+        <v>18</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>246</v>
+        <v>339</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>247</v>
+        <v>18</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>248</v>
+        <v>18</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>254</v>
+        <v>341</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6514,7 +6547,7 @@
         <v>77</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>18</v>
@@ -6523,16 +6556,16 @@
         <v>18</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>91</v>
+        <v>342</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>184</v>
+        <v>343</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>185</v>
+        <v>344</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6583,7 +6616,7 @@
         <v>18</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>186</v>
+        <v>345</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>77</v>
@@ -6592,10 +6625,10 @@
         <v>89</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>187</v>
+        <v>18</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>18</v>
+        <v>101</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>18</v>
@@ -6604,7 +6637,7 @@
         <v>18</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>188</v>
+        <v>134</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>18</v>
@@ -6613,26 +6646,28 @@
         <v>18</v>
       </c>
     </row>
-    <row r="42" hidden="true">
+    <row r="42">
       <c r="A42" t="s" s="2">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="C42" s="2"/>
+        <v>244</v>
+      </c>
+      <c r="C42" t="s" s="2">
+        <v>347</v>
+      </c>
       <c r="D42" t="s" s="2">
-        <v>159</v>
+        <v>245</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>18</v>
@@ -6641,18 +6676,18 @@
         <v>18</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>136</v>
+        <v>247</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>190</v>
+        <v>348</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="O42" s="2"/>
+        <v>249</v>
+      </c>
+      <c r="N42" s="2"/>
+      <c r="O42" t="s" s="2">
+        <v>250</v>
+      </c>
       <c r="P42" t="s" s="2">
         <v>18</v>
       </c>
@@ -6676,31 +6711,29 @@
         <v>18</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="Y42" t="s" s="2">
-        <v>18</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="Y42" s="2"/>
       <c r="Z42" t="s" s="2">
-        <v>18</v>
+        <v>349</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>139</v>
+        <v>18</v>
       </c>
       <c r="AC42" t="s" s="2">
-        <v>192</v>
+        <v>18</v>
       </c>
       <c r="AD42" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>140</v>
+        <v>18</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>193</v>
+        <v>244</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>77</v>
@@ -6712,30 +6745,30 @@
         <v>18</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>142</v>
+        <v>101</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>18</v>
+        <v>255</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>18</v>
+        <v>256</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>188</v>
+        <v>257</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>18</v>
+        <v>258</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>18</v>
+        <v>259</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>341</v>
+        <v>350</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>258</v>
+        <v>265</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6743,7 +6776,7 @@
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="G43" t="s" s="2">
         <v>89</v>
@@ -6755,16 +6788,16 @@
         <v>18</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>259</v>
+        <v>91</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>260</v>
+        <v>195</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>261</v>
+        <v>196</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -6815,7 +6848,7 @@
         <v>18</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>262</v>
+        <v>197</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>77</v>
@@ -6824,10 +6857,10 @@
         <v>89</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>18</v>
+        <v>198</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>101</v>
+        <v>18</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>18</v>
@@ -6836,7 +6869,7 @@
         <v>18</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>134</v>
+        <v>199</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>18</v>
@@ -6847,21 +6880,21 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>342</v>
+        <v>351</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>18</v>
+        <v>170</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>18</v>
@@ -6873,15 +6906,17 @@
         <v>18</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>91</v>
+        <v>137</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>184</v>
+        <v>201</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>185</v>
-      </c>
-      <c r="N44" s="2"/>
+        <v>202</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>173</v>
+      </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>18</v>
@@ -6918,31 +6953,31 @@
         <v>18</v>
       </c>
       <c r="AB44" t="s" s="2">
-        <v>18</v>
+        <v>140</v>
       </c>
       <c r="AC44" t="s" s="2">
-        <v>18</v>
+        <v>203</v>
       </c>
       <c r="AD44" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AE44" t="s" s="2">
-        <v>18</v>
+        <v>141</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>186</v>
+        <v>204</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>187</v>
+        <v>18</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>18</v>
+        <v>143</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>18</v>
@@ -6951,7 +6986,7 @@
         <v>18</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>188</v>
+        <v>199</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>18</v>
@@ -6962,21 +6997,21 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>343</v>
+        <v>352</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>159</v>
+        <v>18</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>18</v>
@@ -6985,20 +7020,18 @@
         <v>18</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>136</v>
+        <v>270</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>190</v>
+        <v>271</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>162</v>
-      </c>
+        <v>272</v>
+      </c>
+      <c r="N45" s="2"/>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>18</v>
@@ -7035,31 +7068,31 @@
         <v>18</v>
       </c>
       <c r="AB45" t="s" s="2">
-        <v>139</v>
+        <v>18</v>
       </c>
       <c r="AC45" t="s" s="2">
-        <v>192</v>
+        <v>18</v>
       </c>
       <c r="AD45" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AE45" t="s" s="2">
-        <v>140</v>
+        <v>18</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>193</v>
+        <v>273</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>142</v>
+        <v>101</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>18</v>
@@ -7068,7 +7101,7 @@
         <v>18</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>188</v>
+        <v>134</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>18</v>
@@ -7079,10 +7112,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>344</v>
+        <v>353</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>268</v>
+        <v>275</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7090,10 +7123,10 @@
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>18</v>
@@ -7102,23 +7135,19 @@
         <v>18</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>269</v>
+        <v>91</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>270</v>
+        <v>195</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>273</v>
-      </c>
+        <v>196</v>
+      </c>
+      <c r="N46" s="2"/>
+      <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>18</v>
       </c>
@@ -7166,19 +7195,19 @@
         <v>18</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>274</v>
+        <v>197</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>18</v>
+        <v>198</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>101</v>
+        <v>18</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>18</v>
@@ -7187,7 +7216,7 @@
         <v>18</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>275</v>
+        <v>199</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>18</v>
@@ -7198,21 +7227,21 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>345</v>
+        <v>354</v>
       </c>
       <c r="B47" t="s" s="2">
         <v>277</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>18</v>
+        <v>170</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>18</v>
@@ -7224,15 +7253,17 @@
         <v>18</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>91</v>
+        <v>137</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>184</v>
+        <v>201</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>185</v>
-      </c>
-      <c r="N47" s="2"/>
+        <v>202</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>173</v>
+      </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>18</v>
@@ -7269,31 +7300,31 @@
         <v>18</v>
       </c>
       <c r="AB47" t="s" s="2">
-        <v>18</v>
+        <v>140</v>
       </c>
       <c r="AC47" t="s" s="2">
-        <v>18</v>
+        <v>203</v>
       </c>
       <c r="AD47" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AE47" t="s" s="2">
-        <v>18</v>
+        <v>141</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>186</v>
+        <v>204</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>187</v>
+        <v>18</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>18</v>
+        <v>143</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>18</v>
@@ -7302,7 +7333,7 @@
         <v>18</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>188</v>
+        <v>199</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>18</v>
@@ -7313,18 +7344,18 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>346</v>
+        <v>355</v>
       </c>
       <c r="B48" t="s" s="2">
         <v>279</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>159</v>
+        <v>18</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="G48" t="s" s="2">
         <v>78</v>
@@ -7336,21 +7367,23 @@
         <v>18</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>136</v>
+        <v>280</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>190</v>
+        <v>281</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>191</v>
+        <v>282</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="O48" s="2"/>
+        <v>283</v>
+      </c>
+      <c r="O48" t="s" s="2">
+        <v>284</v>
+      </c>
       <c r="P48" t="s" s="2">
         <v>18</v>
       </c>
@@ -7386,19 +7419,19 @@
         <v>18</v>
       </c>
       <c r="AB48" t="s" s="2">
-        <v>139</v>
+        <v>18</v>
       </c>
       <c r="AC48" t="s" s="2">
-        <v>192</v>
+        <v>18</v>
       </c>
       <c r="AD48" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AE48" t="s" s="2">
-        <v>140</v>
+        <v>18</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>193</v>
+        <v>285</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>77</v>
@@ -7410,7 +7443,7 @@
         <v>18</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>142</v>
+        <v>101</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>18</v>
@@ -7419,7 +7452,7 @@
         <v>18</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>188</v>
+        <v>286</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>18</v>
@@ -7430,10 +7463,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>347</v>
+        <v>356</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>281</v>
+        <v>288</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7441,7 +7474,7 @@
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="G49" t="s" s="2">
         <v>89</v>
@@ -7453,23 +7486,19 @@
         <v>18</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>282</v>
+        <v>195</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>285</v>
-      </c>
+        <v>196</v>
+      </c>
+      <c r="N49" s="2"/>
+      <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>18</v>
       </c>
@@ -7478,7 +7507,7 @@
         <v>18</v>
       </c>
       <c r="S49" t="s" s="2">
-        <v>348</v>
+        <v>18</v>
       </c>
       <c r="T49" t="s" s="2">
         <v>18</v>
@@ -7517,7 +7546,7 @@
         <v>18</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>287</v>
+        <v>197</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>77</v>
@@ -7526,10 +7555,10 @@
         <v>89</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>18</v>
+        <v>198</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>101</v>
+        <v>18</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>18</v>
@@ -7538,7 +7567,7 @@
         <v>18</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>288</v>
+        <v>199</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>18</v>
@@ -7549,21 +7578,21 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>349</v>
+        <v>357</v>
       </c>
       <c r="B50" t="s" s="2">
         <v>290</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>18</v>
+        <v>170</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>18</v>
@@ -7572,19 +7601,19 @@
         <v>18</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>291</v>
+        <v>137</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>292</v>
+        <v>201</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>293</v>
+        <v>202</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>294</v>
+        <v>173</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -7622,31 +7651,31 @@
         <v>18</v>
       </c>
       <c r="AB50" t="s" s="2">
-        <v>18</v>
+        <v>140</v>
       </c>
       <c r="AC50" t="s" s="2">
-        <v>18</v>
+        <v>203</v>
       </c>
       <c r="AD50" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AE50" t="s" s="2">
-        <v>18</v>
+        <v>141</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>295</v>
+        <v>204</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>101</v>
+        <v>143</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>18</v>
@@ -7655,7 +7684,7 @@
         <v>18</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>296</v>
+        <v>199</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>18</v>
@@ -7666,10 +7695,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>350</v>
+        <v>358</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7677,7 +7706,7 @@
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="G51" t="s" s="2">
         <v>89</v>
@@ -7692,17 +7721,19 @@
         <v>90</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="N51" s="2"/>
+        <v>294</v>
+      </c>
+      <c r="N51" t="s" s="2">
+        <v>295</v>
+      </c>
       <c r="O51" t="s" s="2">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>18</v>
@@ -7712,7 +7743,7 @@
         <v>18</v>
       </c>
       <c r="S51" t="s" s="2">
-        <v>18</v>
+        <v>359</v>
       </c>
       <c r="T51" t="s" s="2">
         <v>18</v>
@@ -7751,7 +7782,7 @@
         <v>18</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>77</v>
@@ -7760,7 +7791,7 @@
         <v>89</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>303</v>
+        <v>18</v>
       </c>
       <c r="AJ51" t="s" s="2">
         <v>101</v>
@@ -7772,7 +7803,7 @@
         <v>18</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>18</v>
@@ -7783,10 +7814,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>351</v>
+        <v>360</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7809,18 +7840,18 @@
         <v>90</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>291</v>
+        <v>302</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="N52" s="2"/>
-      <c r="O52" t="s" s="2">
-        <v>309</v>
-      </c>
+        <v>304</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>18</v>
       </c>
@@ -7868,7 +7899,7 @@
         <v>18</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>77</v>
@@ -7877,7 +7908,7 @@
         <v>89</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>303</v>
+        <v>18</v>
       </c>
       <c r="AJ52" t="s" s="2">
         <v>101</v>
@@ -7889,7 +7920,7 @@
         <v>18</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>18</v>
@@ -7900,10 +7931,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>352</v>
+        <v>361</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7926,19 +7957,17 @@
         <v>90</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>314</v>
+        <v>109</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>316</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>317</v>
-      </c>
+        <v>311</v>
+      </c>
+      <c r="N53" s="2"/>
       <c r="O53" t="s" s="2">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>18</v>
@@ -7987,7 +8016,7 @@
         <v>18</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>77</v>
@@ -7996,7 +8025,7 @@
         <v>89</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>18</v>
+        <v>314</v>
       </c>
       <c r="AJ53" t="s" s="2">
         <v>101</v>
@@ -8008,7 +8037,7 @@
         <v>18</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>18</v>
@@ -8019,10 +8048,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>353</v>
+        <v>362</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8045,19 +8074,17 @@
         <v>90</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>291</v>
+        <v>302</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>325</v>
-      </c>
+        <v>319</v>
+      </c>
+      <c r="N54" s="2"/>
       <c r="O54" t="s" s="2">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>18</v>
@@ -8106,7 +8133,7 @@
         <v>18</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>77</v>
@@ -8115,7 +8142,7 @@
         <v>89</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>18</v>
+        <v>314</v>
       </c>
       <c r="AJ54" t="s" s="2">
         <v>101</v>
@@ -8127,7 +8154,7 @@
         <v>18</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>18</v>
@@ -8138,10 +8165,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>354</v>
+        <v>363</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8152,7 +8179,7 @@
         <v>77</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>18</v>
@@ -8164,16 +8191,20 @@
         <v>90</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>333</v>
-      </c>
-      <c r="N55" s="2"/>
-      <c r="O55" s="2"/>
+        <v>327</v>
+      </c>
+      <c r="N55" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="O55" t="s" s="2">
+        <v>329</v>
+      </c>
       <c r="P55" t="s" s="2">
         <v>18</v>
       </c>
@@ -8221,7 +8252,7 @@
         <v>18</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>77</v>
@@ -8242,7 +8273,7 @@
         <v>18</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>134</v>
+        <v>331</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>18</v>
@@ -8253,10 +8284,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>355</v>
+        <v>364</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>355</v>
+        <v>333</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8276,19 +8307,23 @@
         <v>18</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>259</v>
+        <v>302</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>356</v>
+        <v>334</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="N56" s="2"/>
-      <c r="O56" s="2"/>
+        <v>335</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="O56" t="s" s="2">
+        <v>337</v>
+      </c>
       <c r="P56" t="s" s="2">
         <v>18</v>
       </c>
@@ -8312,13 +8347,13 @@
         <v>18</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>240</v>
+        <v>18</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>358</v>
+        <v>18</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>359</v>
+        <v>18</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>18</v>
@@ -8336,7 +8371,7 @@
         <v>18</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>355</v>
+        <v>338</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>77</v>
@@ -8351,27 +8386,27 @@
         <v>101</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>360</v>
+        <v>18</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>245</v>
+        <v>18</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>361</v>
+        <v>339</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>247</v>
+        <v>18</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>362</v>
+        <v>18</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>363</v>
+        <v>341</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8382,7 +8417,7 @@
         <v>77</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>18</v>
@@ -8391,16 +8426,16 @@
         <v>18</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>364</v>
+        <v>342</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>365</v>
+        <v>343</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>366</v>
+        <v>344</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -8451,13 +8486,13 @@
         <v>18</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>363</v>
+        <v>345</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>18</v>
@@ -8466,16 +8501,16 @@
         <v>101</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>360</v>
+        <v>18</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>245</v>
+        <v>18</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>361</v>
+        <v>134</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>247</v>
+        <v>18</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>18</v>
@@ -8483,10 +8518,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8509,18 +8544,16 @@
         <v>18</v>
       </c>
       <c r="K58" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="L58" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="M58" t="s" s="2">
         <v>368</v>
       </c>
-      <c r="L58" t="s" s="2">
-        <v>369</v>
-      </c>
-      <c r="M58" t="s" s="2">
-        <v>370</v>
-      </c>
       <c r="N58" s="2"/>
-      <c r="O58" t="s" s="2">
-        <v>371</v>
-      </c>
+      <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>18</v>
       </c>
@@ -8544,13 +8577,13 @@
         <v>18</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>18</v>
+        <v>251</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>18</v>
+        <v>369</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>18</v>
+        <v>370</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>18</v>
@@ -8568,7 +8601,7 @@
         <v>18</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>77</v>
@@ -8583,27 +8616,27 @@
         <v>101</v>
       </c>
       <c r="AK58" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="AL58" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="AM58" t="s" s="2">
         <v>372</v>
       </c>
-      <c r="AL58" t="s" s="2">
+      <c r="AN58" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="AO58" t="s" s="2">
         <v>373</v>
-      </c>
-      <c r="AM58" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="AN58" t="s" s="2">
-        <v>375</v>
-      </c>
-      <c r="AO58" t="s" s="2">
-        <v>18</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8614,7 +8647,7 @@
         <v>77</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>18</v>
@@ -8626,13 +8659,13 @@
         <v>18</v>
       </c>
       <c r="K59" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="L59" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="M59" t="s" s="2">
         <v>377</v>
-      </c>
-      <c r="L59" t="s" s="2">
-        <v>378</v>
-      </c>
-      <c r="M59" t="s" s="2">
-        <v>379</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -8683,13 +8716,13 @@
         <v>18</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>18</v>
@@ -8698,27 +8731,27 @@
         <v>101</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>360</v>
+        <v>371</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>245</v>
+        <v>256</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>361</v>
+        <v>372</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>247</v>
+        <v>258</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>18</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8726,34 +8759,32 @@
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="H60" t="s" s="2">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="I60" t="s" s="2">
         <v>18</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="K60" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="L60" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="M60" t="s" s="2">
         <v>381</v>
       </c>
-      <c r="L60" t="s" s="2">
+      <c r="N60" s="2"/>
+      <c r="O60" t="s" s="2">
         <v>382</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="O60" t="s" s="2">
-        <v>385</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>18</v>
@@ -8802,42 +8833,42 @@
         <v>18</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="AG60" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ60" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK60" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="AL60" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="AM60" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="AN60" t="s" s="2">
         <v>386</v>
       </c>
-      <c r="AK60" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="AL60" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="AM60" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="AN60" t="s" s="2">
-        <v>390</v>
-      </c>
       <c r="AO60" t="s" s="2">
-        <v>391</v>
+        <v>18</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8860,13 +8891,13 @@
         <v>18</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>291</v>
+        <v>388</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>184</v>
+        <v>389</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>185</v>
+        <v>390</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -8917,7 +8948,7 @@
         <v>18</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>186</v>
+        <v>387</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>77</v>
@@ -8926,67 +8957,69 @@
         <v>89</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>187</v>
+        <v>18</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>18</v>
+        <v>101</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>18</v>
+        <v>371</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>18</v>
+        <v>256</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>188</v>
+        <v>372</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>18</v>
+        <v>258</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>18</v>
       </c>
     </row>
-    <row r="62" hidden="true">
+    <row r="62">
       <c r="A62" t="s" s="2">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>159</v>
+        <v>18</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="G62" t="s" s="2">
         <v>78</v>
       </c>
       <c r="H62" t="s" s="2">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="I62" t="s" s="2">
         <v>18</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>136</v>
+        <v>392</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>190</v>
+        <v>393</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>191</v>
+        <v>394</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="O62" s="2"/>
+        <v>395</v>
+      </c>
+      <c r="O62" t="s" s="2">
+        <v>396</v>
+      </c>
       <c r="P62" t="s" s="2">
         <v>18</v>
       </c>
@@ -9034,10 +9067,10 @@
         <v>18</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>193</v>
+        <v>391</v>
       </c>
       <c r="AG62" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="AH62" t="s" s="2">
         <v>78</v>
@@ -9046,66 +9079,62 @@
         <v>18</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>142</v>
+        <v>397</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>18</v>
+        <v>398</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>18</v>
+        <v>399</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>188</v>
+        <v>400</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>18</v>
+        <v>401</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>18</v>
+        <v>402</v>
       </c>
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>394</v>
+        <v>403</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>394</v>
+        <v>403</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>395</v>
+        <v>18</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>18</v>
       </c>
       <c r="I63" t="s" s="2">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>136</v>
+        <v>302</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>396</v>
+        <v>195</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="O63" t="s" s="2">
-        <v>163</v>
-      </c>
+        <v>196</v>
+      </c>
+      <c r="N63" s="2"/>
+      <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>18</v>
       </c>
@@ -9153,19 +9182,19 @@
         <v>18</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>398</v>
+        <v>197</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>18</v>
+        <v>198</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>142</v>
+        <v>18</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>18</v>
@@ -9174,7 +9203,7 @@
         <v>18</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>134</v>
+        <v>199</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>18</v>
@@ -9185,21 +9214,21 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>18</v>
+        <v>170</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>18</v>
@@ -9208,23 +9237,21 @@
         <v>18</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>259</v>
+        <v>137</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>400</v>
+        <v>201</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>401</v>
+        <v>202</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="O64" t="s" s="2">
-        <v>403</v>
-      </c>
+        <v>173</v>
+      </c>
+      <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>18</v>
       </c>
@@ -9248,13 +9275,13 @@
         <v>18</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>240</v>
+        <v>18</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>404</v>
+        <v>18</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>405</v>
+        <v>18</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>18</v>
@@ -9272,46 +9299,46 @@
         <v>18</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>399</v>
+        <v>204</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>101</v>
+        <v>143</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>406</v>
+        <v>18</v>
       </c>
       <c r="AL64" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>407</v>
+        <v>199</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>408</v>
+        <v>18</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>409</v>
+        <v>18</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>18</v>
+        <v>406</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
@@ -9324,25 +9351,25 @@
         <v>18</v>
       </c>
       <c r="I65" t="s" s="2">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>259</v>
+        <v>137</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>413</v>
+        <v>173</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>414</v>
+        <v>174</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>18</v>
@@ -9367,13 +9394,13 @@
         <v>18</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>240</v>
+        <v>18</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>415</v>
+        <v>18</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>416</v>
+        <v>18</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>18</v>
@@ -9391,7 +9418,7 @@
         <v>18</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>77</v>
@@ -9403,7 +9430,7 @@
         <v>18</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>101</v>
+        <v>143</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>18</v>
@@ -9412,21 +9439,21 @@
         <v>18</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>417</v>
+        <v>134</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>418</v>
+        <v>18</v>
       </c>
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>419</v>
+        <v>410</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>419</v>
+        <v>410</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9434,7 +9461,7 @@
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="G66" t="s" s="2">
         <v>89</v>
@@ -9449,16 +9476,20 @@
         <v>90</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>420</v>
+        <v>270</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>421</v>
+        <v>411</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="N66" s="2"/>
-      <c r="O66" s="2"/>
+        <v>412</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="O66" t="s" s="2">
+        <v>414</v>
+      </c>
       <c r="P66" t="s" s="2">
         <v>18</v>
       </c>
@@ -9482,13 +9513,13 @@
         <v>18</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>18</v>
+        <v>251</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>18</v>
+        <v>415</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>18</v>
+        <v>416</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>18</v>
@@ -9506,42 +9537,42 @@
         <v>18</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>419</v>
+        <v>410</v>
       </c>
       <c r="AG66" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="AH66" t="s" s="2">
         <v>89</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>423</v>
+        <v>18</v>
       </c>
       <c r="AJ66" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>424</v>
+        <v>417</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>425</v>
+        <v>18</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>426</v>
+        <v>418</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>18</v>
+        <v>419</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>18</v>
+        <v>420</v>
       </c>
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9552,7 +9583,7 @@
         <v>77</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>18</v>
@@ -9564,16 +9595,20 @@
         <v>18</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>428</v>
+        <v>270</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="N67" s="2"/>
-      <c r="O67" s="2"/>
+        <v>423</v>
+      </c>
+      <c r="N67" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="O67" t="s" s="2">
+        <v>425</v>
+      </c>
       <c r="P67" t="s" s="2">
         <v>18</v>
       </c>
@@ -9597,13 +9632,13 @@
         <v>18</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>18</v>
+        <v>251</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>18</v>
+        <v>426</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>18</v>
+        <v>427</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>18</v>
@@ -9621,16 +9656,16 @@
         <v>18</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>423</v>
+        <v>18</v>
       </c>
       <c r="AJ67" t="s" s="2">
         <v>101</v>
@@ -9642,21 +9677,21 @@
         <v>18</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>18</v>
+        <v>429</v>
       </c>
     </row>
-    <row r="68">
+    <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9667,10 +9702,10 @@
         <v>89</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="H68" t="s" s="2">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="I68" t="s" s="2">
         <v>18</v>
@@ -9679,13 +9714,13 @@
         <v>90</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>381</v>
+        <v>431</v>
       </c>
       <c r="L68" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="M68" t="s" s="2">
         <v>433</v>
-      </c>
-      <c r="M68" t="s" s="2">
-        <v>434</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -9736,34 +9771,34 @@
         <v>18</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="AG68" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>18</v>
+        <v>434</v>
       </c>
       <c r="AJ68" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>18</v>
+        <v>435</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>18</v>
+        <v>436</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>436</v>
+        <v>18</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>437</v>
+        <v>18</v>
       </c>
     </row>
     <row r="69" hidden="true">
@@ -9794,13 +9829,13 @@
         <v>18</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>291</v>
+        <v>439</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>184</v>
+        <v>440</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>185</v>
+        <v>441</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -9851,7 +9886,7 @@
         <v>18</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>186</v>
+        <v>438</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>77</v>
@@ -9860,10 +9895,10 @@
         <v>89</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>187</v>
+        <v>434</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>18</v>
+        <v>101</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>18</v>
@@ -9872,7 +9907,7 @@
         <v>18</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>188</v>
+        <v>442</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>18</v>
@@ -9881,45 +9916,43 @@
         <v>18</v>
       </c>
     </row>
-    <row r="70" hidden="true">
+    <row r="70">
       <c r="A70" t="s" s="2">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>159</v>
+        <v>18</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="G70" t="s" s="2">
         <v>78</v>
       </c>
       <c r="H70" t="s" s="2">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="I70" t="s" s="2">
         <v>18</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>136</v>
+        <v>392</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>190</v>
+        <v>444</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>162</v>
-      </c>
+        <v>445</v>
+      </c>
+      <c r="N70" s="2"/>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>18</v>
@@ -9968,7 +10001,7 @@
         <v>18</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>193</v>
+        <v>443</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>77</v>
@@ -9980,7 +10013,7 @@
         <v>18</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>142</v>
+        <v>101</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>18</v>
@@ -9989,57 +10022,53 @@
         <v>18</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>188</v>
+        <v>446</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>18</v>
+        <v>447</v>
       </c>
       <c r="AO70" t="s" s="2">
-        <v>18</v>
+        <v>448</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>440</v>
+        <v>449</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>440</v>
+        <v>449</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>395</v>
+        <v>18</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>18</v>
       </c>
       <c r="I71" t="s" s="2">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>136</v>
+        <v>302</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>396</v>
+        <v>195</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="O71" t="s" s="2">
-        <v>163</v>
-      </c>
+        <v>196</v>
+      </c>
+      <c r="N71" s="2"/>
+      <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
         <v>18</v>
       </c>
@@ -10087,19 +10116,19 @@
         <v>18</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>398</v>
+        <v>197</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AI71" t="s" s="2">
-        <v>18</v>
+        <v>198</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>142</v>
+        <v>18</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>18</v>
@@ -10108,7 +10137,7 @@
         <v>18</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>134</v>
+        <v>199</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>18</v>
@@ -10119,21 +10148,21 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>441</v>
+        <v>450</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>441</v>
+        <v>450</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>18</v>
+        <v>170</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>18</v>
@@ -10142,18 +10171,20 @@
         <v>18</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>109</v>
+        <v>137</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>442</v>
+        <v>201</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="N72" s="2"/>
+        <v>202</v>
+      </c>
+      <c r="N72" t="s" s="2">
+        <v>173</v>
+      </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
         <v>18</v>
@@ -10163,7 +10194,7 @@
         <v>18</v>
       </c>
       <c r="S72" t="s" s="2">
-        <v>444</v>
+        <v>18</v>
       </c>
       <c r="T72" t="s" s="2">
         <v>18</v>
@@ -10178,13 +10209,13 @@
         <v>18</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>113</v>
+        <v>18</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>445</v>
+        <v>18</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>446</v>
+        <v>18</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>18</v>
@@ -10202,19 +10233,19 @@
         <v>18</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>441</v>
+        <v>204</v>
       </c>
       <c r="AG72" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>101</v>
+        <v>143</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>18</v>
@@ -10223,55 +10254,57 @@
         <v>18</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>447</v>
+        <v>199</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>448</v>
+        <v>18</v>
       </c>
       <c r="AO72" t="s" s="2">
-        <v>449</v>
+        <v>18</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>18</v>
+        <v>406</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>18</v>
       </c>
       <c r="I73" t="s" s="2">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="J73" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>451</v>
+        <v>137</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>452</v>
+        <v>407</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>453</v>
+        <v>408</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>454</v>
-      </c>
-      <c r="O73" s="2"/>
+        <v>173</v>
+      </c>
+      <c r="O73" t="s" s="2">
+        <v>174</v>
+      </c>
       <c r="P73" t="s" s="2">
         <v>18</v>
       </c>
@@ -10319,19 +10352,19 @@
         <v>18</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>450</v>
+        <v>409</v>
       </c>
       <c r="AG73" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>101</v>
+        <v>143</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>18</v>
@@ -10340,21 +10373,21 @@
         <v>18</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>455</v>
+        <v>134</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>375</v>
+        <v>18</v>
       </c>
       <c r="AO73" t="s" s="2">
-        <v>173</v>
+        <v>18</v>
       </c>
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10362,10 +10395,10 @@
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>18</v>
@@ -10374,20 +10407,18 @@
         <v>18</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>79</v>
+        <v>109</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>458</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>459</v>
-      </c>
+        <v>454</v>
+      </c>
+      <c r="N74" s="2"/>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
         <v>18</v>
@@ -10397,7 +10428,7 @@
         <v>18</v>
       </c>
       <c r="S74" t="s" s="2">
-        <v>18</v>
+        <v>455</v>
       </c>
       <c r="T74" t="s" s="2">
         <v>18</v>
@@ -10412,13 +10443,13 @@
         <v>18</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>18</v>
+        <v>113</v>
       </c>
       <c r="Y74" t="s" s="2">
-        <v>18</v>
+        <v>456</v>
       </c>
       <c r="Z74" t="s" s="2">
-        <v>18</v>
+        <v>457</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>18</v>
@@ -10436,13 +10467,13 @@
         <v>18</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="AG74" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AI74" t="s" s="2">
         <v>18</v>
@@ -10457,21 +10488,21 @@
         <v>18</v>
       </c>
       <c r="AM74" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="AN74" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="AO74" t="s" s="2">
         <v>460</v>
-      </c>
-      <c r="AN74" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AO74" t="s" s="2">
-        <v>461</v>
       </c>
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10479,10 +10510,10 @@
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>18</v>
@@ -10491,18 +10522,20 @@
         <v>18</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="K75" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="L75" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="M75" t="s" s="2">
         <v>463</v>
       </c>
-      <c r="L75" t="s" s="2">
+      <c r="N75" t="s" s="2">
         <v>464</v>
       </c>
-      <c r="M75" t="s" s="2">
-        <v>465</v>
-      </c>
-      <c r="N75" s="2"/>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
         <v>18</v>
@@ -10551,13 +10584,13 @@
         <v>18</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="AG75" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AI75" t="s" s="2">
         <v>18</v>
@@ -10572,17 +10605,249 @@
         <v>18</v>
       </c>
       <c r="AM75" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="AN75" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="AO75" t="s" s="2">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="76" hidden="true">
+      <c r="A76" t="s" s="2">
         <v>466</v>
       </c>
-      <c r="AN75" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AO75" t="s" s="2">
+      <c r="B76" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="C76" s="2"/>
+      <c r="D76" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="E76" s="2"/>
+      <c r="F76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G76" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H76" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I76" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J76" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="K76" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="L76" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="M76" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="N76" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="O76" s="2"/>
+      <c r="P76" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Q76" s="2"/>
+      <c r="R76" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="S76" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="T76" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="U76" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="V76" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="W76" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="X76" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Y76" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Z76" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AA76" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AB76" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AC76" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AD76" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AE76" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AF76" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="AG76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH76" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI76" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AJ76" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK76" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AL76" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AM76" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="AN76" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AO76" t="s" s="2">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="77" hidden="true">
+      <c r="A77" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="B77" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="C77" s="2"/>
+      <c r="D77" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="E77" s="2"/>
+      <c r="F77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H77" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I77" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J77" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="K77" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="L77" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="M77" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="N77" s="2"/>
+      <c r="O77" s="2"/>
+      <c r="P77" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Q77" s="2"/>
+      <c r="R77" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="S77" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="T77" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="U77" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="V77" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="W77" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="X77" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Y77" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Z77" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AA77" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AB77" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AC77" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AD77" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AE77" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AF77" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="AG77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI77" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AJ77" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK77" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AL77" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AM77" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="AN77" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AO77" t="s" s="2">
         <v>18</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO75">
+  <autoFilter ref="A1:AO77">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -10592,7 +10857,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI74">
+  <conditionalFormatting sqref="A2:AI76">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>
